--- a/market/2026-06-kwork-market-fit-CANON.xlsx
+++ b/market/2026-06-kwork-market-fit-CANON.xlsx
@@ -4,18 +4,20 @@
   <workbookPr/>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Orders" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Directions" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ServiceCards" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debts" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Живой слой 16.06" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Orders" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Directions" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ServiceCards" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debts" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Orders'!$A$1:$Y$80</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Directions'!$A$1:$P$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'ServiceCards'!$A$1:$L$230</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Sources'!$A$1:$G$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Debts'!$A$1:$E$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Живой слой 16.06'!$A$1:$N$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Orders'!$A$1:$Y$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Directions'!$A$1:$P$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'ServiceCards'!$A$1:$L$230</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Sources'!$A$1:$J$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Debts'!$A$1:$E$7</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -471,6 +473,12 @@
     <xf numFmtId="1" fontId="8" fillId="6" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="9" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -478,12 +486,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="8" fillId="6" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="10" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -496,7 +498,29 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF274E13"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD9EAD3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF990000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="1"/>
@@ -835,7 +859,7 @@
     <row r="2" ht="15" customHeight="1" s="14">
       <c r="A2" s="66" t="inlineStr">
         <is>
-          <t>одна книга: спрос, направления, кворки, источники, долги</t>
+          <t>LIVE отдельно, канон отдельно, источники отдельно</t>
         </is>
       </c>
       <c r="B2" s="67" t="str"/>
@@ -897,12 +921,12 @@
         </is>
       </c>
       <c r="B6" s="71">
-        <f>COUNTIF(Orders!B:B,"LIVE")+COUNTIF(Orders!B:B,"LIVE+CODEX")</f>
+        <f>COUNTA('Живой слой 16.06'!A2:A46)</f>
         <v/>
       </c>
       <c r="C6" s="71" t="inlineStr">
         <is>
-          <t>LIVE source layer</t>
+          <t>лист Живой слой 16.06</t>
         </is>
       </c>
       <c r="D6" s="71" t="n"/>
@@ -916,12 +940,12 @@
         </is>
       </c>
       <c r="B7" s="71">
-        <f>COUNTIFS(Orders!B:B,"LIVE",Orders!P:P,"low")+COUNTIFS(Orders!B:B,"LIVE+CODEX",Orders!P:P,"low")</f>
+        <f>COUNTIF('Живой слой 16.06'!L2:L46,"low")</f>
         <v/>
       </c>
       <c r="C7" s="71" t="inlineStr">
         <is>
-          <t>offers &lt;= 5 or live band low</t>
+          <t>competition=low на live-листе</t>
         </is>
       </c>
       <c r="D7" s="71" t="n"/>
@@ -1289,6 +1313,3353 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" style="14" min="1" max="1"/>
+    <col width="9" customWidth="1" style="14" min="2" max="2"/>
+    <col width="44" customWidth="1" style="14" min="3" max="3"/>
+    <col width="9" customWidth="1" style="14" min="4" max="4"/>
+    <col width="15" customWidth="1" style="14" min="5" max="5"/>
+    <col width="12" customWidth="1" style="14" min="6" max="6"/>
+    <col width="12" customWidth="1" style="14" min="7" max="7"/>
+    <col width="9" customWidth="1" style="14" min="8" max="8"/>
+    <col width="9" customWidth="1" style="14" min="9" max="9"/>
+    <col width="9" customWidth="1" style="14" min="10" max="10"/>
+    <col width="9" customWidth="1" style="14" min="11" max="11"/>
+    <col width="13" customWidth="1" style="14" min="12" max="12"/>
+    <col width="26" customWidth="1" style="14" min="13" max="13"/>
+    <col width="42" customWidth="1" style="14" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1" s="14">
+      <c r="A1" s="72" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="72" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="72" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="D1" s="72" t="inlineStr">
+        <is>
+          <t>lane</t>
+        </is>
+      </c>
+      <c r="E1" s="72" t="inlineStr">
+        <is>
+          <t>niche</t>
+        </is>
+      </c>
+      <c r="F1" s="72" t="inlineStr">
+        <is>
+          <t>budget_min</t>
+        </is>
+      </c>
+      <c r="G1" s="72" t="inlineStr">
+        <is>
+          <t>budget_max</t>
+        </is>
+      </c>
+      <c r="H1" s="72" t="inlineStr">
+        <is>
+          <t>offers</t>
+        </is>
+      </c>
+      <c r="I1" s="72" t="inlineStr">
+        <is>
+          <t>views</t>
+        </is>
+      </c>
+      <c r="J1" s="72" t="inlineStr">
+        <is>
+          <t>days</t>
+        </is>
+      </c>
+      <c r="K1" s="72" t="inlineStr">
+        <is>
+          <t>cat_id</t>
+        </is>
+      </c>
+      <c r="L1" s="72" t="inlineStr">
+        <is>
+          <t>competition</t>
+        </is>
+      </c>
+      <c r="M1" s="72" t="inlineStr">
+        <is>
+          <t>source_kw</t>
+        </is>
+      </c>
+      <c r="N1" s="72" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1" s="14">
+      <c r="A2" s="73" t="inlineStr">
+        <is>
+          <t>3198791</t>
+        </is>
+      </c>
+      <c r="B2" s="73" t="inlineStr">
+        <is>
+          <t>16 июня</t>
+        </is>
+      </c>
+      <c r="C2" s="73" t="inlineStr">
+        <is>
+          <t>1С Автосервис - доработка</t>
+        </is>
+      </c>
+      <c r="D2" s="73" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E2" s="73" t="inlineStr">
+        <is>
+          <t>1c</t>
+        </is>
+      </c>
+      <c r="F2" s="74" t="inlineStr">
+        <is>
+          <t>7000</t>
+        </is>
+      </c>
+      <c r="G2" s="74" t="inlineStr">
+        <is>
+          <t>21000</t>
+        </is>
+      </c>
+      <c r="H2" s="75" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I2" s="75" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="J2" s="73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K2" s="73" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="L2" s="73" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="M2" s="73" t="inlineStr">
+        <is>
+          <t>1с</t>
+        </is>
+      </c>
+      <c r="N2" s="73" t="inlineStr">
+        <is>
+          <t>живой 16.06 - мало откликов хороший вход</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1" s="14">
+      <c r="A3" s="71" t="inlineStr">
+        <is>
+          <t>3198119</t>
+        </is>
+      </c>
+      <c r="B3" s="71" t="inlineStr">
+        <is>
+          <t>15 июня</t>
+        </is>
+      </c>
+      <c r="C3" s="71" t="inlineStr">
+        <is>
+          <t>Руководство как в 1С УНФ сделать контракты</t>
+        </is>
+      </c>
+      <c r="D3" s="71" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E3" s="71" t="inlineStr">
+        <is>
+          <t>1c</t>
+        </is>
+      </c>
+      <c r="F3" s="76" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="G3" s="76" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="H3" s="77" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I3" s="77" t="inlineStr">
+        <is>
+          <t>912</t>
+        </is>
+      </c>
+      <c r="J3" s="71" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K3" s="71" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="L3" s="71" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="M3" s="71" t="inlineStr">
+        <is>
+          <t>акт сверки</t>
+        </is>
+      </c>
+      <c r="N3" s="71" t="inlineStr">
+        <is>
+          <t>высокий просмотр документная задача</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="14">
+      <c r="A4" s="73" t="inlineStr">
+        <is>
+          <t>3196862</t>
+        </is>
+      </c>
+      <c r="B4" s="73" t="inlineStr">
+        <is>
+          <t>14 июня</t>
+        </is>
+      </c>
+      <c r="C4" s="73" t="inlineStr">
+        <is>
+          <t>Программа учета для магазина автозапчастей на 1с</t>
+        </is>
+      </c>
+      <c r="D4" s="73" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E4" s="73" t="inlineStr">
+        <is>
+          <t>1c</t>
+        </is>
+      </c>
+      <c r="F4" s="74" t="inlineStr">
+        <is>
+          <t>60000</t>
+        </is>
+      </c>
+      <c r="G4" s="74" t="inlineStr">
+        <is>
+          <t>180000</t>
+        </is>
+      </c>
+      <c r="H4" s="75" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="I4" s="75" t="inlineStr">
+        <is>
+          <t>708</t>
+        </is>
+      </c>
+      <c r="J4" s="73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K4" s="73" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="L4" s="73" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="M4" s="73" t="inlineStr">
+        <is>
+          <t>учет</t>
+        </is>
+      </c>
+      <c r="N4" s="73" t="inlineStr">
+        <is>
+          <t>крупный бюджет 1С-разработка</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="14">
+      <c r="A5" s="71" t="inlineStr">
+        <is>
+          <t>3198286</t>
+        </is>
+      </c>
+      <c r="B5" s="71" t="inlineStr">
+        <is>
+          <t>16 июня</t>
+        </is>
+      </c>
+      <c r="C5" s="71" t="inlineStr">
+        <is>
+          <t>Восстановление бух учета СБИС/Сабy</t>
+        </is>
+      </c>
+      <c r="D5" s="71" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E5" s="71" t="inlineStr">
+        <is>
+          <t>accounting</t>
+        </is>
+      </c>
+      <c r="F5" s="76" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="G5" s="76" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="H5" s="77" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I5" s="77" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="J5" s="71" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K5" s="71" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="L5" s="71" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="M5" s="71" t="inlineStr">
+        <is>
+          <t>осв</t>
+        </is>
+      </c>
+      <c r="N5" s="71" t="inlineStr">
+        <is>
+          <t>редкий чистый бух-заказ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="14">
+      <c r="A6" s="73" t="inlineStr">
+        <is>
+          <t>3198627</t>
+        </is>
+      </c>
+      <c r="B6" s="73" t="inlineStr">
+        <is>
+          <t>16 июня</t>
+        </is>
+      </c>
+      <c r="C6" s="73" t="inlineStr">
+        <is>
+          <t>Удаленный Бухгалтер</t>
+        </is>
+      </c>
+      <c r="D6" s="73" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E6" s="73" t="inlineStr">
+        <is>
+          <t>accounting</t>
+        </is>
+      </c>
+      <c r="F6" s="74" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="G6" s="74" t="inlineStr">
+        <is>
+          <t>12000</t>
+        </is>
+      </c>
+      <c r="H6" s="75" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I6" s="75" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="J6" s="73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K6" s="73" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="L6" s="73" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="M6" s="73" t="inlineStr">
+        <is>
+          <t>бухгалтер</t>
+        </is>
+      </c>
+      <c r="N6" s="73" t="inlineStr">
+        <is>
+          <t>единственный активный по «бухгалтер»</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="14">
+      <c r="A7" s="71" t="inlineStr">
+        <is>
+          <t>3198647</t>
+        </is>
+      </c>
+      <c r="B7" s="71" t="inlineStr">
+        <is>
+          <t>16 июня</t>
+        </is>
+      </c>
+      <c r="C7" s="71" t="inlineStr">
+        <is>
+          <t>Разработка стиля карточек и витрины для маркетплейсов</t>
+        </is>
+      </c>
+      <c r="D7" s="71" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E7" s="71" t="inlineStr">
+        <is>
+          <t>marketplace</t>
+        </is>
+      </c>
+      <c r="F7" s="76" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="G7" s="76" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="H7" s="77" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="I7" s="77" t="inlineStr">
+        <is>
+          <t>579</t>
+        </is>
+      </c>
+      <c r="J7" s="71" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K7" s="71" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="L7" s="71" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="M7" s="71" t="inlineStr">
+        <is>
+          <t>маркетплейс</t>
+        </is>
+      </c>
+      <c r="N7" s="71" t="inlineStr">
+        <is>
+          <t>дизайн+контент МП</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="14">
+      <c r="A8" s="73" t="inlineStr">
+        <is>
+          <t>3197828</t>
+        </is>
+      </c>
+      <c r="B8" s="73" t="inlineStr">
+        <is>
+          <t>15 июня</t>
+        </is>
+      </c>
+      <c r="C8" s="73" t="inlineStr">
+        <is>
+          <t>Создание контента для маркетплейсов с помощью ИИ</t>
+        </is>
+      </c>
+      <c r="D8" s="73" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E8" s="73" t="inlineStr">
+        <is>
+          <t>marketplace</t>
+        </is>
+      </c>
+      <c r="F8" s="74" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="G8" s="74" t="inlineStr">
+        <is>
+          <t>15000</t>
+        </is>
+      </c>
+      <c r="H8" s="75" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="I8" s="75" t="inlineStr">
+        <is>
+          <t>1219</t>
+        </is>
+      </c>
+      <c r="J8" s="73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K8" s="73" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="L8" s="73" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M8" s="73" t="inlineStr">
+        <is>
+          <t>маркетплейс</t>
+        </is>
+      </c>
+      <c r="N8" s="73" t="inlineStr">
+        <is>
+          <t>красный океан ИИ-контент</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="14">
+      <c r="A9" s="71" t="inlineStr">
+        <is>
+          <t>3198518</t>
+        </is>
+      </c>
+      <c r="B9" s="71" t="inlineStr">
+        <is>
+          <t>16 июня</t>
+        </is>
+      </c>
+      <c r="C9" s="71" t="inlineStr">
+        <is>
+          <t>Карточка товара</t>
+        </is>
+      </c>
+      <c r="D9" s="71" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E9" s="71" t="inlineStr">
+        <is>
+          <t>marketplace</t>
+        </is>
+      </c>
+      <c r="F9" s="76" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="G9" s="76" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="H9" s="77" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="I9" s="77" t="inlineStr">
+        <is>
+          <t>838</t>
+        </is>
+      </c>
+      <c r="J9" s="71" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K9" s="71" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="L9" s="71" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M9" s="71" t="inlineStr">
+        <is>
+          <t>маркетплейс</t>
+        </is>
+      </c>
+      <c r="N9" s="71" t="inlineStr">
+        <is>
+          <t>commodity 125 откликов</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" s="14">
+      <c r="A10" s="73" t="inlineStr">
+        <is>
+          <t>3198710</t>
+        </is>
+      </c>
+      <c r="B10" s="73" t="inlineStr">
+        <is>
+          <t>16 июня</t>
+        </is>
+      </c>
+      <c r="C10" s="73" t="inlineStr">
+        <is>
+          <t>Написать ядро сборщика из карточек товара (парсер)</t>
+        </is>
+      </c>
+      <c r="D10" s="73" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E10" s="73" t="inlineStr">
+        <is>
+          <t>parsing</t>
+        </is>
+      </c>
+      <c r="F10" s="74" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="G10" s="74" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="H10" s="75" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I10" s="75" t="inlineStr">
+        <is>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="J10" s="73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K10" s="73" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="L10" s="73" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="M10" s="73" t="inlineStr">
+        <is>
+          <t>маркетплейс</t>
+        </is>
+      </c>
+      <c r="N10" s="73" t="inlineStr">
+        <is>
+          <t>парсинг МП - зона Влада</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1" s="14">
+      <c r="A11" s="71" t="inlineStr">
+        <is>
+          <t>3197613</t>
+        </is>
+      </c>
+      <c r="B11" s="71" t="inlineStr">
+        <is>
+          <t>15 июня</t>
+        </is>
+      </c>
+      <c r="C11" s="71" t="inlineStr">
+        <is>
+          <t>Плачу % за привлечение селлеров WB/Ozon</t>
+        </is>
+      </c>
+      <c r="D11" s="71" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E11" s="71" t="inlineStr">
+        <is>
+          <t>leadgen</t>
+        </is>
+      </c>
+      <c r="F11" s="76" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="G11" s="76" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="H11" s="77" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I11" s="77" t="inlineStr">
+        <is>
+          <t>493</t>
+        </is>
+      </c>
+      <c r="J11" s="71" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K11" s="71" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="L11" s="71" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="M11" s="71" t="inlineStr">
+        <is>
+          <t>маркетплейс</t>
+        </is>
+      </c>
+      <c r="N11" s="71" t="inlineStr">
+        <is>
+          <t>партнёрка не наша</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1" s="14">
+      <c r="A12" s="73" t="inlineStr">
+        <is>
+          <t>3198376</t>
+        </is>
+      </c>
+      <c r="B12" s="73" t="inlineStr">
+        <is>
+          <t>16 июня</t>
+        </is>
+      </c>
+      <c r="C12" s="73" t="inlineStr">
+        <is>
+          <t>Перепечатать данные из рукописного журнала в Excel</t>
+        </is>
+      </c>
+      <c r="D12" s="73" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E12" s="73" t="inlineStr">
+        <is>
+          <t>excel-entry</t>
+        </is>
+      </c>
+      <c r="F12" s="74" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="G12" s="74" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="H12" s="75" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="I12" s="75" t="inlineStr">
+        <is>
+          <t>997</t>
+        </is>
+      </c>
+      <c r="J12" s="73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K12" s="73" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="L12" s="73" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M12" s="73" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="N12" s="73" t="inlineStr">
+        <is>
+          <t>ручной ввод - не брать</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1" s="14">
+      <c r="A13" s="71" t="inlineStr">
+        <is>
+          <t>3198005</t>
+        </is>
+      </c>
+      <c r="B13" s="71" t="inlineStr">
+        <is>
+          <t>15 июня</t>
+        </is>
+      </c>
+      <c r="C13" s="71" t="inlineStr">
+        <is>
+          <t>PDF в Excel</t>
+        </is>
+      </c>
+      <c r="D13" s="71" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E13" s="71" t="inlineStr">
+        <is>
+          <t>excel-entry</t>
+        </is>
+      </c>
+      <c r="F13" s="76" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="G13" s="76" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="H13" s="77" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="I13" s="77" t="inlineStr">
+        <is>
+          <t>1862</t>
+        </is>
+      </c>
+      <c r="J13" s="71" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K13" s="71" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="L13" s="71" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M13" s="71" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="N13" s="71" t="inlineStr">
+        <is>
+          <t>327 откликов commodity</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1" s="14">
+      <c r="A14" s="73" t="inlineStr">
+        <is>
+          <t>3198558</t>
+        </is>
+      </c>
+      <c r="B14" s="73" t="inlineStr">
+        <is>
+          <t>16 июня</t>
+        </is>
+      </c>
+      <c r="C14" s="73" t="inlineStr">
+        <is>
+          <t>Собрать базу организаций для обзвона</t>
+        </is>
+      </c>
+      <c r="D14" s="73" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E14" s="73" t="inlineStr">
+        <is>
+          <t>data-excel</t>
+        </is>
+      </c>
+      <c r="F14" s="74" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="G14" s="74" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="H14" s="75" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I14" s="75" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="J14" s="73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K14" s="73" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="L14" s="73" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="M14" s="73" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="N14" s="73" t="inlineStr">
+        <is>
+          <t>парсинг+таблица</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1" s="14">
+      <c r="A15" s="71" t="inlineStr">
+        <is>
+          <t>3198019</t>
+        </is>
+      </c>
+      <c r="B15" s="71" t="inlineStr">
+        <is>
+          <t>15 июня</t>
+        </is>
+      </c>
+      <c r="C15" s="71" t="inlineStr">
+        <is>
+          <t>Сбор/парсинг Telegram-каналов: бьюти</t>
+        </is>
+      </c>
+      <c r="D15" s="71" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E15" s="71" t="inlineStr">
+        <is>
+          <t>parsing</t>
+        </is>
+      </c>
+      <c r="F15" s="76" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="G15" s="76" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="H15" s="77" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I15" s="77" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="J15" s="71" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K15" s="71" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="L15" s="71" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="M15" s="71" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="N15" s="71" t="inlineStr">
+        <is>
+          <t>дешёвый парсинг</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="14">
+      <c r="A16" s="73" t="inlineStr">
+        <is>
+          <t>3198339</t>
+        </is>
+      </c>
+      <c r="B16" s="73" t="inlineStr">
+        <is>
+          <t>16 июня</t>
+        </is>
+      </c>
+      <c r="C16" s="73" t="inlineStr">
+        <is>
+          <t>Сделать отчёт по посещаемости</t>
+        </is>
+      </c>
+      <c r="D16" s="73" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E16" s="73" t="inlineStr">
+        <is>
+          <t>data-excel</t>
+        </is>
+      </c>
+      <c r="F16" s="74" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="G16" s="74" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="H16" s="75" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I16" s="75" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="J16" s="73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K16" s="73" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="L16" s="73" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="M16" s="73" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="N16" s="73" t="inlineStr">
+        <is>
+          <t>таблица-отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1" s="14">
+      <c r="A17" s="71" t="inlineStr">
+        <is>
+          <t>3198621</t>
+        </is>
+      </c>
+      <c r="B17" s="71" t="inlineStr">
+        <is>
+          <t>16 июня</t>
+        </is>
+      </c>
+      <c r="C17" s="71" t="inlineStr">
+        <is>
+          <t>Нужна выгрузка компаний по г. Москва</t>
+        </is>
+      </c>
+      <c r="D17" s="71" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E17" s="71" t="inlineStr">
+        <is>
+          <t>parsing</t>
+        </is>
+      </c>
+      <c r="F17" s="76" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="G17" s="76" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="H17" s="77" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I17" s="77" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="J17" s="71" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K17" s="71" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="L17" s="71" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="M17" s="71" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="N17" s="71" t="inlineStr">
+        <is>
+          <t>парсинг+выгрузка</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1" s="14">
+      <c r="A18" s="73" t="inlineStr">
+        <is>
+          <t>3198707</t>
+        </is>
+      </c>
+      <c r="B18" s="73" t="inlineStr">
+        <is>
+          <t>16 июня</t>
+        </is>
+      </c>
+      <c r="C18" s="73" t="inlineStr">
+        <is>
+          <t>Заключить 99 договоров с кадровыми агентствами</t>
+        </is>
+      </c>
+      <c r="D18" s="73" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E18" s="73" t="inlineStr">
+        <is>
+          <t>leadgen</t>
+        </is>
+      </c>
+      <c r="F18" s="74" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="G18" s="74" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="H18" s="75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I18" s="75" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="J18" s="73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K18" s="73" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="L18" s="73" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="M18" s="73" t="inlineStr">
+        <is>
+          <t>коммерческое предложение</t>
+        </is>
+      </c>
+      <c r="N18" s="73" t="inlineStr">
+        <is>
+          <t>холодный обзвон не наш</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1" s="14">
+      <c r="A19" s="71" t="inlineStr">
+        <is>
+          <t>3198248</t>
+        </is>
+      </c>
+      <c r="B19" s="71" t="inlineStr">
+        <is>
+          <t>15 июня</t>
+        </is>
+      </c>
+      <c r="C19" s="71" t="inlineStr">
+        <is>
+          <t>Разработка шаблона оформления кейсов компании</t>
+        </is>
+      </c>
+      <c r="D19" s="71" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E19" s="71" t="inlineStr">
+        <is>
+          <t>kp-b2b</t>
+        </is>
+      </c>
+      <c r="F19" s="76" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="G19" s="76" t="inlineStr">
+        <is>
+          <t>12000</t>
+        </is>
+      </c>
+      <c r="H19" s="77" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I19" s="77" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="J19" s="71" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K19" s="71" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="L19" s="71" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="M19" s="71" t="inlineStr">
+        <is>
+          <t>коммерческое предложение</t>
+        </is>
+      </c>
+      <c r="N19" s="71" t="inlineStr">
+        <is>
+          <t>упаковка кейсов - зона Влада</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1" s="14">
+      <c r="A20" s="73" t="inlineStr">
+        <is>
+          <t>3197922</t>
+        </is>
+      </c>
+      <c r="B20" s="73" t="inlineStr">
+        <is>
+          <t>15 июня</t>
+        </is>
+      </c>
+      <c r="C20" s="73" t="inlineStr">
+        <is>
+          <t>Поиск B2B клиентов для маркетингового агентства</t>
+        </is>
+      </c>
+      <c r="D20" s="73" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E20" s="73" t="inlineStr">
+        <is>
+          <t>kp-b2b</t>
+        </is>
+      </c>
+      <c r="F20" s="74" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="G20" s="74" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="H20" s="75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I20" s="75" t="inlineStr">
+        <is>
+          <t>573</t>
+        </is>
+      </c>
+      <c r="J20" s="73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K20" s="73" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="L20" s="73" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="M20" s="73" t="inlineStr">
+        <is>
+          <t>коммерческое предложение</t>
+        </is>
+      </c>
+      <c r="N20" s="73" t="inlineStr">
+        <is>
+          <t>B2B продажи мало откликов</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1" s="14">
+      <c r="A21" s="71" t="inlineStr">
+        <is>
+          <t>3197935</t>
+        </is>
+      </c>
+      <c r="B21" s="71" t="inlineStr">
+        <is>
+          <t>15 июня</t>
+        </is>
+      </c>
+      <c r="C21" s="71" t="inlineStr">
+        <is>
+          <t>Корпоративный мессенджер для компании</t>
+        </is>
+      </c>
+      <c r="D21" s="71" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E21" s="71" t="inlineStr">
+        <is>
+          <t>crm-bitrix</t>
+        </is>
+      </c>
+      <c r="F21" s="76" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="G21" s="76" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="H21" s="77" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I21" s="77" t="inlineStr">
+        <is>
+          <t>556</t>
+        </is>
+      </c>
+      <c r="J21" s="71" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K21" s="71" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="L21" s="71" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="M21" s="71" t="inlineStr">
+        <is>
+          <t>коммерческое предложение</t>
+        </is>
+      </c>
+      <c r="N21" s="71" t="inlineStr">
+        <is>
+          <t>крупная разработка</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1" s="14">
+      <c r="A22" s="73" t="inlineStr">
+        <is>
+          <t>3195348</t>
+        </is>
+      </c>
+      <c r="B22" s="73" t="inlineStr">
+        <is>
+          <t>11 июня</t>
+        </is>
+      </c>
+      <c r="C22" s="73" t="inlineStr">
+        <is>
+          <t>Техническое задание на проектирование бани</t>
+        </is>
+      </c>
+      <c r="D22" s="73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E22" s="73" t="inlineStr">
+        <is>
+          <t>tz</t>
+        </is>
+      </c>
+      <c r="F22" s="74" t="inlineStr">
+        <is>
+          <t>7000</t>
+        </is>
+      </c>
+      <c r="G22" s="74" t="inlineStr">
+        <is>
+          <t>21000</t>
+        </is>
+      </c>
+      <c r="H22" s="75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I22" s="75" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="J22" s="73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K22" s="73" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="L22" s="73" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="M22" s="73" t="inlineStr">
+        <is>
+          <t>техническое задание</t>
+        </is>
+      </c>
+      <c r="N22" s="73" t="inlineStr">
+        <is>
+          <t>ТЗ=стройка не IT</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1" s="14">
+      <c r="A23" s="71" t="inlineStr">
+        <is>
+          <t>3198330</t>
+        </is>
+      </c>
+      <c r="B23" s="71" t="inlineStr">
+        <is>
+          <t>16 июня</t>
+        </is>
+      </c>
+      <c r="C23" s="71" t="inlineStr">
+        <is>
+          <t>Разработать интернет-магазин (сайт уже есть)</t>
+        </is>
+      </c>
+      <c r="D23" s="71" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E23" s="71" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="F23" s="76" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="G23" s="76" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="H23" s="77" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="I23" s="77" t="inlineStr">
+        <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="J23" s="71" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K23" s="71" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="L23" s="71" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="M23" s="71" t="inlineStr">
+        <is>
+          <t>техническое задание</t>
+        </is>
+      </c>
+      <c r="N23" s="71" t="inlineStr">
+        <is>
+          <t>e-commerce доработка</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1" s="14">
+      <c r="A24" s="73" t="inlineStr">
+        <is>
+          <t>3197965</t>
+        </is>
+      </c>
+      <c r="B24" s="73" t="inlineStr">
+        <is>
+          <t>15 июня</t>
+        </is>
+      </c>
+      <c r="C24" s="73" t="inlineStr">
+        <is>
+          <t>Провести SEO-аудит и подготовить план</t>
+        </is>
+      </c>
+      <c r="D24" s="73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E24" s="73" t="inlineStr">
+        <is>
+          <t>seo</t>
+        </is>
+      </c>
+      <c r="F24" s="74" t="inlineStr">
+        <is>
+          <t>15000</t>
+        </is>
+      </c>
+      <c r="G24" s="74" t="inlineStr">
+        <is>
+          <t>45000</t>
+        </is>
+      </c>
+      <c r="H24" s="75" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="I24" s="75" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="J24" s="73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K24" s="73" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="L24" s="73" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="M24" s="73" t="inlineStr">
+        <is>
+          <t>техническое задание</t>
+        </is>
+      </c>
+      <c r="N24" s="73" t="inlineStr">
+        <is>
+          <t>не наша ниша</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" s="14">
+      <c r="A25" s="71" t="inlineStr">
+        <is>
+          <t>3196048</t>
+        </is>
+      </c>
+      <c r="B25" s="71" t="inlineStr">
+        <is>
+          <t>12 июня</t>
+        </is>
+      </c>
+      <c r="C25" s="71" t="inlineStr">
+        <is>
+          <t>Разработать аналог сайта + парсинг/наполнение</t>
+        </is>
+      </c>
+      <c r="D25" s="71" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E25" s="71" t="inlineStr">
+        <is>
+          <t>parsing</t>
+        </is>
+      </c>
+      <c r="F25" s="76" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="G25" s="76" t="inlineStr">
+        <is>
+          <t>90000</t>
+        </is>
+      </c>
+      <c r="H25" s="77" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="I25" s="77" t="inlineStr">
+        <is>
+          <t>1706</t>
+        </is>
+      </c>
+      <c r="J25" s="71" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K25" s="71" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="L25" s="71" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="M25" s="71" t="inlineStr">
+        <is>
+          <t>парсинг</t>
+        </is>
+      </c>
+      <c r="N25" s="71" t="inlineStr">
+        <is>
+          <t>крупный парсинг+сайт</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1" s="14">
+      <c r="A26" s="73" t="inlineStr">
+        <is>
+          <t>2545228</t>
+        </is>
+      </c>
+      <c r="B26" s="73" t="inlineStr">
+        <is>
+          <t>архив</t>
+        </is>
+      </c>
+      <c r="C26" s="73" t="inlineStr">
+        <is>
+          <t>Доработка парсера</t>
+        </is>
+      </c>
+      <c r="D26" s="73" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E26" s="73" t="inlineStr">
+        <is>
+          <t>parsing</t>
+        </is>
+      </c>
+      <c r="F26" s="74" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="G26" s="74" t="inlineStr">
+        <is>
+          <t>90000</t>
+        </is>
+      </c>
+      <c r="H26" s="75" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="I26" s="75" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="J26" s="73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K26" s="73" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="L26" s="73" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="M26" s="73" t="inlineStr">
+        <is>
+          <t>парсинг</t>
+        </is>
+      </c>
+      <c r="N26" s="73" t="inlineStr">
+        <is>
+          <t>старый но активный</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1" s="14">
+      <c r="A27" s="71" t="inlineStr">
+        <is>
+          <t>3198468</t>
+        </is>
+      </c>
+      <c r="B27" s="71" t="inlineStr">
+        <is>
+          <t>16 июня</t>
+        </is>
+      </c>
+      <c r="C27" s="71" t="inlineStr">
+        <is>
+          <t>Разработка асинхронного Python парсера для AmoCRM</t>
+        </is>
+      </c>
+      <c r="D27" s="71" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E27" s="71" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="F27" s="76" t="inlineStr">
+        <is>
+          <t>7000</t>
+        </is>
+      </c>
+      <c r="G27" s="76" t="inlineStr">
+        <is>
+          <t>21000</t>
+        </is>
+      </c>
+      <c r="H27" s="77" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I27" s="77" t="inlineStr">
+        <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="J27" s="71" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K27" s="71" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="L27" s="71" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="M27" s="71" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="N27" s="71" t="inlineStr">
+        <is>
+          <t>идеальная зона Влада</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="14">
+      <c r="A28" s="73" t="inlineStr">
+        <is>
+          <t>3195831</t>
+        </is>
+      </c>
+      <c r="B28" s="73" t="inlineStr">
+        <is>
+          <t>12 июня</t>
+        </is>
+      </c>
+      <c r="C28" s="73" t="inlineStr">
+        <is>
+          <t>Изучить скрипты Python и устранить ошибки</t>
+        </is>
+      </c>
+      <c r="D28" s="73" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E28" s="73" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="F28" s="74" t="inlineStr">
+        <is>
+          <t>12000</t>
+        </is>
+      </c>
+      <c r="G28" s="74" t="inlineStr">
+        <is>
+          <t>36000</t>
+        </is>
+      </c>
+      <c r="H28" s="75" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I28" s="75" t="inlineStr">
+        <is>
+          <t>1113</t>
+        </is>
+      </c>
+      <c r="J28" s="73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K28" s="73" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="L28" s="73" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M28" s="73" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="N28" s="73" t="inlineStr">
+        <is>
+          <t>много откликов «почини скрипт»</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1" s="14">
+      <c r="A29" s="71" t="inlineStr">
+        <is>
+          <t>3198488</t>
+        </is>
+      </c>
+      <c r="B29" s="71" t="inlineStr">
+        <is>
+          <t>16 июня</t>
+        </is>
+      </c>
+      <c r="C29" s="71" t="inlineStr">
+        <is>
+          <t>Дополнить робота по автоответам на Ozon</t>
+        </is>
+      </c>
+      <c r="D29" s="71" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E29" s="71" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="F29" s="76" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="G29" s="76" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="H29" s="77" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I29" s="77" t="inlineStr">
+        <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="J29" s="71" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K29" s="71" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="L29" s="71" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="M29" s="71" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="N29" s="71" t="inlineStr">
+        <is>
+          <t>дешёвый но много откликов</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1" s="14">
+      <c r="A30" s="73" t="inlineStr">
+        <is>
+          <t>3197770</t>
+        </is>
+      </c>
+      <c r="B30" s="73" t="inlineStr">
+        <is>
+          <t>15 июня</t>
+        </is>
+      </c>
+      <c r="C30" s="73" t="inlineStr">
+        <is>
+          <t>Доработка отчётов в DataLence</t>
+        </is>
+      </c>
+      <c r="D30" s="73" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E30" s="73" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="F30" s="74" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="G30" s="74" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="H30" s="75" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="I30" s="75" t="inlineStr">
+        <is>
+          <t>711</t>
+        </is>
+      </c>
+      <c r="J30" s="73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K30" s="73" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="L30" s="73" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="M30" s="73" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="N30" s="73" t="inlineStr">
+        <is>
+          <t>BI/данные</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1" s="14">
+      <c r="A31" s="71" t="inlineStr">
+        <is>
+          <t>3198201</t>
+        </is>
+      </c>
+      <c r="B31" s="71" t="inlineStr">
+        <is>
+          <t>15 июня</t>
+        </is>
+      </c>
+      <c r="C31" s="71" t="inlineStr">
+        <is>
+          <t>Создать телеграмм бот</t>
+        </is>
+      </c>
+      <c r="D31" s="71" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E31" s="71" t="inlineStr">
+        <is>
+          <t>tg-bot</t>
+        </is>
+      </c>
+      <c r="F31" s="76" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="G31" s="76" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="H31" s="77" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="I31" s="77" t="inlineStr">
+        <is>
+          <t>1053</t>
+        </is>
+      </c>
+      <c r="J31" s="71" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K31" s="71" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="L31" s="71" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M31" s="71" t="inlineStr">
+        <is>
+          <t>телеграм бот</t>
+        </is>
+      </c>
+      <c r="N31" s="71" t="inlineStr">
+        <is>
+          <t>демпинг 500₽ 87 откликов</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1" s="14">
+      <c r="A32" s="73" t="inlineStr">
+        <is>
+          <t>3197646</t>
+        </is>
+      </c>
+      <c r="B32" s="73" t="inlineStr">
+        <is>
+          <t>15 июня</t>
+        </is>
+      </c>
+      <c r="C32" s="73" t="inlineStr">
+        <is>
+          <t>Доработка бота в Salebot для ВК и ТГ</t>
+        </is>
+      </c>
+      <c r="D32" s="73" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E32" s="73" t="inlineStr">
+        <is>
+          <t>tg-bot</t>
+        </is>
+      </c>
+      <c r="F32" s="74" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="G32" s="74" t="inlineStr">
+        <is>
+          <t>15000</t>
+        </is>
+      </c>
+      <c r="H32" s="75" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="I32" s="75" t="inlineStr">
+        <is>
+          <t>857</t>
+        </is>
+      </c>
+      <c r="J32" s="73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K32" s="73" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="L32" s="73" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="M32" s="73" t="inlineStr">
+        <is>
+          <t>телеграм бот</t>
+        </is>
+      </c>
+      <c r="N32" s="73" t="inlineStr">
+        <is>
+          <t>доработка конструктора</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1" s="14">
+      <c r="A33" s="71" t="inlineStr">
+        <is>
+          <t>3197238</t>
+        </is>
+      </c>
+      <c r="B33" s="71" t="inlineStr">
+        <is>
+          <t>14 июня</t>
+        </is>
+      </c>
+      <c r="C33" s="71" t="inlineStr">
+        <is>
+          <t>AI бот для MAX и TG + интеграция платёжной системы</t>
+        </is>
+      </c>
+      <c r="D33" s="71" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E33" s="71" t="inlineStr">
+        <is>
+          <t>ai-bot</t>
+        </is>
+      </c>
+      <c r="F33" s="76" t="inlineStr">
+        <is>
+          <t>50000</t>
+        </is>
+      </c>
+      <c r="G33" s="76" t="inlineStr">
+        <is>
+          <t>150000</t>
+        </is>
+      </c>
+      <c r="H33" s="77" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="I33" s="77" t="inlineStr">
+        <is>
+          <t>890</t>
+        </is>
+      </c>
+      <c r="J33" s="71" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K33" s="71" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="L33" s="71" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="M33" s="71" t="inlineStr">
+        <is>
+          <t>телеграм бот</t>
+        </is>
+      </c>
+      <c r="N33" s="71" t="inlineStr">
+        <is>
+          <t>крупный AI-бот высокий спрос</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1" s="14">
+      <c r="A34" s="73" t="inlineStr">
+        <is>
+          <t>3197479</t>
+        </is>
+      </c>
+      <c r="B34" s="73" t="inlineStr">
+        <is>
+          <t>15 июня</t>
+        </is>
+      </c>
+      <c r="C34" s="73" t="inlineStr">
+        <is>
+          <t>ИИ бот для наблюдения за видеокамерами</t>
+        </is>
+      </c>
+      <c r="D34" s="73" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E34" s="73" t="inlineStr">
+        <is>
+          <t>ai-bot</t>
+        </is>
+      </c>
+      <c r="F34" s="74" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="G34" s="74" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="H34" s="75" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="I34" s="75" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="J34" s="73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K34" s="73" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="L34" s="73" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="M34" s="73" t="inlineStr">
+        <is>
+          <t>телеграм бот</t>
+        </is>
+      </c>
+      <c r="N34" s="73" t="inlineStr">
+        <is>
+          <t>CV/AI крупный бюджет</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1" s="14">
+      <c r="A35" s="71" t="inlineStr">
+        <is>
+          <t>3198567</t>
+        </is>
+      </c>
+      <c r="B35" s="71" t="inlineStr">
+        <is>
+          <t>16 июня</t>
+        </is>
+      </c>
+      <c r="C35" s="71" t="inlineStr">
+        <is>
+          <t>Исправить ошибки в работе бота</t>
+        </is>
+      </c>
+      <c r="D35" s="71" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E35" s="71" t="inlineStr">
+        <is>
+          <t>tg-bot</t>
+        </is>
+      </c>
+      <c r="F35" s="76" t="inlineStr">
+        <is>
+          <t>6500</t>
+        </is>
+      </c>
+      <c r="G35" s="76" t="inlineStr">
+        <is>
+          <t>19500</t>
+        </is>
+      </c>
+      <c r="H35" s="77" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="I35" s="77" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="J35" s="71" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K35" s="71" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="L35" s="71" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="M35" s="71" t="inlineStr">
+        <is>
+          <t>телеграм бот</t>
+        </is>
+      </c>
+      <c r="N35" s="71" t="inlineStr">
+        <is>
+          <t>фикс-задача</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1" s="14">
+      <c r="A36" s="73" t="inlineStr">
+        <is>
+          <t>3198141</t>
+        </is>
+      </c>
+      <c r="B36" s="73" t="inlineStr">
+        <is>
+          <t>15 июня</t>
+        </is>
+      </c>
+      <c r="C36" s="73" t="inlineStr">
+        <is>
+          <t>Настройка Битрикс24 Облако для стоматологии</t>
+        </is>
+      </c>
+      <c r="D36" s="73" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E36" s="73" t="inlineStr">
+        <is>
+          <t>crm-bitrix</t>
+        </is>
+      </c>
+      <c r="F36" s="74" t="inlineStr">
+        <is>
+          <t>40000</t>
+        </is>
+      </c>
+      <c r="G36" s="74" t="inlineStr">
+        <is>
+          <t>120000</t>
+        </is>
+      </c>
+      <c r="H36" s="75" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I36" s="75" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
+      </c>
+      <c r="J36" s="73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K36" s="73" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="L36" s="73" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="M36" s="73" t="inlineStr">
+        <is>
+          <t>учет</t>
+        </is>
+      </c>
+      <c r="N36" s="73" t="inlineStr">
+        <is>
+          <t>CRM-настройка</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1" s="14">
+      <c r="A37" s="71" t="inlineStr">
+        <is>
+          <t>3198694</t>
+        </is>
+      </c>
+      <c r="B37" s="71" t="inlineStr">
+        <is>
+          <t>16 июня</t>
+        </is>
+      </c>
+      <c r="C37" s="71" t="inlineStr">
+        <is>
+          <t>Автоматизация отчётов и анализа рекламных кабинетов VK</t>
+        </is>
+      </c>
+      <c r="D37" s="71" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E37" s="71" t="inlineStr">
+        <is>
+          <t>mkt-analytics</t>
+        </is>
+      </c>
+      <c r="F37" s="76" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="G37" s="76" t="inlineStr">
+        <is>
+          <t>90000</t>
+        </is>
+      </c>
+      <c r="H37" s="77" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I37" s="77" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="J37" s="71" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K37" s="71" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="L37" s="71" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="M37" s="71" t="inlineStr">
+        <is>
+          <t>финансовый анализ</t>
+        </is>
+      </c>
+      <c r="N37" s="71" t="inlineStr">
+        <is>
+          <t>автоматизация отчётности</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1" s="14">
+      <c r="A38" s="73" t="inlineStr">
+        <is>
+          <t>3198370</t>
+        </is>
+      </c>
+      <c r="B38" s="73" t="inlineStr">
+        <is>
+          <t>16 июня</t>
+        </is>
+      </c>
+      <c r="C38" s="73" t="inlineStr">
+        <is>
+          <t>Анализ записей телефонных разговоров с ИИ</t>
+        </is>
+      </c>
+      <c r="D38" s="73" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E38" s="73" t="inlineStr">
+        <is>
+          <t>ai-bot</t>
+        </is>
+      </c>
+      <c r="F38" s="74" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="G38" s="74" t="inlineStr">
+        <is>
+          <t>15000</t>
+        </is>
+      </c>
+      <c r="H38" s="75" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I38" s="75" t="inlineStr">
+        <is>
+          <t>454</t>
+        </is>
+      </c>
+      <c r="J38" s="73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K38" s="73" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="L38" s="73" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="M38" s="73" t="inlineStr">
+        <is>
+          <t>финансовый анализ</t>
+        </is>
+      </c>
+      <c r="N38" s="73" t="inlineStr">
+        <is>
+          <t>AI-обработка речи</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1" s="14">
+      <c r="A39" s="71" t="inlineStr">
+        <is>
+          <t>3192226</t>
+        </is>
+      </c>
+      <c r="B39" s="71" t="inlineStr">
+        <is>
+          <t>6 июня</t>
+        </is>
+      </c>
+      <c r="C39" s="71" t="inlineStr">
+        <is>
+          <t>Поиск заказов (для агентства)</t>
+        </is>
+      </c>
+      <c r="D39" s="71" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E39" s="71" t="inlineStr">
+        <is>
+          <t>leadgen</t>
+        </is>
+      </c>
+      <c r="F39" s="76" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="G39" s="76" t="inlineStr">
+        <is>
+          <t>90000</t>
+        </is>
+      </c>
+      <c r="H39" s="77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I39" s="77" t="inlineStr">
+        <is>
+          <t>1136</t>
+        </is>
+      </c>
+      <c r="J39" s="71" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K39" s="71" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="L39" s="71" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="M39" s="71" t="inlineStr">
+        <is>
+          <t>c=83</t>
+        </is>
+      </c>
+      <c r="N39" s="71" t="inlineStr">
+        <is>
+          <t>не наша</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1" s="14">
+      <c r="A40" s="73" t="inlineStr">
+        <is>
+          <t>3198732</t>
+        </is>
+      </c>
+      <c r="B40" s="73" t="inlineStr">
+        <is>
+          <t>16 июня</t>
+        </is>
+      </c>
+      <c r="C40" s="73" t="inlineStr">
+        <is>
+          <t>Поиск каналов продаж для агентства недвижимости</t>
+        </is>
+      </c>
+      <c r="D40" s="73" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E40" s="73" t="inlineStr">
+        <is>
+          <t>kp-b2b</t>
+        </is>
+      </c>
+      <c r="F40" s="74" t="inlineStr">
+        <is>
+          <t>25000</t>
+        </is>
+      </c>
+      <c r="G40" s="74" t="inlineStr">
+        <is>
+          <t>75000</t>
+        </is>
+      </c>
+      <c r="H40" s="75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I40" s="75" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="J40" s="73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K40" s="73" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="L40" s="73" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="M40" s="73" t="inlineStr">
+        <is>
+          <t>c=83</t>
+        </is>
+      </c>
+      <c r="N40" s="73" t="inlineStr">
+        <is>
+          <t>GTM-консалтинг мало откликов</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1" s="14">
+      <c r="A41" s="71" t="inlineStr">
+        <is>
+          <t>3186308</t>
+        </is>
+      </c>
+      <c r="B41" s="71" t="inlineStr">
+        <is>
+          <t>29 мая</t>
+        </is>
+      </c>
+      <c r="C41" s="71" t="inlineStr">
+        <is>
+          <t>Требуется вёрстка нескольких страниц (Figma→HTML)</t>
+        </is>
+      </c>
+      <c r="D41" s="71" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E41" s="71" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="F41" s="76" t="inlineStr">
+        <is>
+          <t>20000</t>
+        </is>
+      </c>
+      <c r="G41" s="76" t="inlineStr">
+        <is>
+          <t>60000</t>
+        </is>
+      </c>
+      <c r="H41" s="77" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I41" s="77" t="inlineStr">
+        <is>
+          <t>1040</t>
+        </is>
+      </c>
+      <c r="J41" s="71" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K41" s="71" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="L41" s="71" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="M41" s="71" t="inlineStr">
+        <is>
+          <t>c=11</t>
+        </is>
+      </c>
+      <c r="N41" s="71" t="inlineStr">
+        <is>
+          <t>вёрстка мало откликов</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1" s="14">
+      <c r="A42" s="73" t="inlineStr">
+        <is>
+          <t>3198797</t>
+        </is>
+      </c>
+      <c r="B42" s="73" t="inlineStr">
+        <is>
+          <t>16 июня</t>
+        </is>
+      </c>
+      <c r="C42" s="73" t="inlineStr">
+        <is>
+          <t>Редактирование сценария oktell</t>
+        </is>
+      </c>
+      <c r="D42" s="73" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E42" s="73" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="F42" s="74" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="G42" s="74" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="H42" s="75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I42" s="75" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="J42" s="73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K42" s="73" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="L42" s="73" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="M42" s="73" t="inlineStr">
+        <is>
+          <t>c=11</t>
+        </is>
+      </c>
+      <c r="N42" s="73" t="inlineStr">
+        <is>
+          <t>телефония-скрипт ноль откликов</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1" s="14">
+      <c r="A43" s="71" t="inlineStr">
+        <is>
+          <t>3198790</t>
+        </is>
+      </c>
+      <c r="B43" s="71" t="inlineStr">
+        <is>
+          <t>16 июня</t>
+        </is>
+      </c>
+      <c r="C43" s="71" t="inlineStr">
+        <is>
+          <t>Создать одностраничный сайт</t>
+        </is>
+      </c>
+      <c r="D43" s="71" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E43" s="71" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="F43" s="76" t="inlineStr">
+        <is>
+          <t>15000</t>
+        </is>
+      </c>
+      <c r="G43" s="76" t="inlineStr">
+        <is>
+          <t>45000</t>
+        </is>
+      </c>
+      <c r="H43" s="77" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I43" s="77" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="J43" s="71" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K43" s="71" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="L43" s="71" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="M43" s="71" t="inlineStr">
+        <is>
+          <t>feed</t>
+        </is>
+      </c>
+      <c r="N43" s="71" t="inlineStr">
+        <is>
+          <t>лендинг конкурентно</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1" s="14">
+      <c r="A44" s="73" t="inlineStr">
+        <is>
+          <t>3198782</t>
+        </is>
+      </c>
+      <c r="B44" s="73" t="inlineStr">
+        <is>
+          <t>16 июня</t>
+        </is>
+      </c>
+      <c r="C44" s="73" t="inlineStr">
+        <is>
+          <t>Поддержка и развитие портала Битрикс24</t>
+        </is>
+      </c>
+      <c r="D44" s="73" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E44" s="73" t="inlineStr">
+        <is>
+          <t>crm-bitrix</t>
+        </is>
+      </c>
+      <c r="F44" s="74" t="inlineStr">
+        <is>
+          <t>25000</t>
+        </is>
+      </c>
+      <c r="G44" s="74" t="inlineStr">
+        <is>
+          <t>75000</t>
+        </is>
+      </c>
+      <c r="H44" s="75" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I44" s="75" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="J44" s="73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K44" s="73" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="L44" s="73" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="M44" s="73" t="inlineStr">
+        <is>
+          <t>feed</t>
+        </is>
+      </c>
+      <c r="N44" s="73" t="inlineStr">
+        <is>
+          <t>поддержка CRM мало откликов</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1" s="14">
+      <c r="A45" s="71" t="inlineStr">
+        <is>
+          <t>3197747</t>
+        </is>
+      </c>
+      <c r="B45" s="71" t="inlineStr">
+        <is>
+          <t>15 июня</t>
+        </is>
+      </c>
+      <c r="C45" s="71" t="inlineStr">
+        <is>
+          <t>Анализ Google Ads (хостелы/отели)</t>
+        </is>
+      </c>
+      <c r="D45" s="71" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E45" s="71" t="inlineStr">
+        <is>
+          <t>mkt-analytics</t>
+        </is>
+      </c>
+      <c r="F45" s="76" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="G45" s="76" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="H45" s="77" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I45" s="77" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="J45" s="71" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K45" s="71" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="L45" s="71" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="M45" s="71" t="inlineStr">
+        <is>
+          <t>финансовый анализ</t>
+        </is>
+      </c>
+      <c r="N45" s="71" t="inlineStr">
+        <is>
+          <t>маркетинг-аналитика</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1" s="14">
+      <c r="A46" s="73" t="inlineStr">
+        <is>
+          <t>3195547</t>
+        </is>
+      </c>
+      <c r="B46" s="73" t="inlineStr">
+        <is>
+          <t>11 июня</t>
+        </is>
+      </c>
+      <c r="C46" s="73" t="inlineStr">
+        <is>
+          <t>Анализ конкурентов</t>
+        </is>
+      </c>
+      <c r="D46" s="73" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E46" s="73" t="inlineStr">
+        <is>
+          <t>mkt-analytics</t>
+        </is>
+      </c>
+      <c r="F46" s="74" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="G46" s="74" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="H46" s="75" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="I46" s="75" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="J46" s="73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K46" s="73" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="L46" s="73" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="M46" s="73" t="inlineStr">
+        <is>
+          <t>финансовый анализ</t>
+        </is>
+      </c>
+      <c r="N46" s="73" t="inlineStr">
+        <is>
+          <t>конкурентный анализ</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:N46"/>
+  <conditionalFormatting sqref="L2:L46">
+    <cfRule type="containsText" priority="1" operator="containsText" dxfId="0" text="low"/>
+    <cfRule type="containsText" priority="2" operator="containsText" dxfId="1" text="red"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1526,12 +4897,12 @@
           <t>912</t>
         </is>
       </c>
-      <c r="P2" s="76" t="inlineStr">
+      <c r="P2" s="78" t="inlineStr">
         <is>
           <t>mid</t>
         </is>
       </c>
-      <c r="Q2" s="77" t="inlineStr">
+      <c r="Q2" s="79" t="inlineStr">
         <is>
           <t>TAKE</t>
         </is>
@@ -1546,7 +4917,7 @@
           <t>med</t>
         </is>
       </c>
-      <c r="T2" s="78" t="inlineStr">
+      <c r="T2" s="80" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -1627,26 +4998,26 @@
           <t>AI, боты, CRM</t>
         </is>
       </c>
-      <c r="K3" s="79" t="inlineStr">
+      <c r="K3" s="76" t="inlineStr">
         <is>
           <t>5000</t>
         </is>
       </c>
-      <c r="L3" s="79" t="inlineStr">
+      <c r="L3" s="76" t="inlineStr">
         <is>
           <t>15000</t>
         </is>
       </c>
-      <c r="M3" s="79">
+      <c r="M3" s="76">
         <f>IF(AND(K3&lt;&gt;"",L3&lt;&gt;""),(K3+L3)/2,"")</f>
         <v/>
       </c>
-      <c r="N3" s="80" t="inlineStr">
+      <c r="N3" s="77" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="O3" s="80" t="inlineStr">
+      <c r="O3" s="77" t="inlineStr">
         <is>
           <t>857</t>
         </is>
@@ -1656,7 +5027,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="Q3" s="77" t="inlineStr">
+      <c r="Q3" s="79" t="inlineStr">
         <is>
           <t>TAKE WITH SCOPE</t>
         </is>
@@ -1676,7 +5047,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="U3" s="79">
+      <c r="U3" s="76">
         <f>IF(AND(M3&lt;&gt;"",T3&lt;&gt;""),M3/T3,"")</f>
         <v/>
       </c>
@@ -1776,12 +5147,12 @@
           <t>634</t>
         </is>
       </c>
-      <c r="P4" s="76" t="inlineStr">
+      <c r="P4" s="78" t="inlineStr">
         <is>
           <t>mid</t>
         </is>
       </c>
-      <c r="Q4" s="77" t="inlineStr">
+      <c r="Q4" s="79" t="inlineStr">
         <is>
           <t>TAKE</t>
         </is>
@@ -1796,7 +5167,7 @@
           <t>med</t>
         </is>
       </c>
-      <c r="T4" s="78" t="inlineStr">
+      <c r="T4" s="80" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -1877,36 +5248,36 @@
           <t>Excel и таблицы</t>
         </is>
       </c>
-      <c r="K5" s="79" t="inlineStr">
+      <c r="K5" s="76" t="inlineStr">
         <is>
           <t>1500</t>
         </is>
       </c>
-      <c r="L5" s="79" t="inlineStr">
+      <c r="L5" s="76" t="inlineStr">
         <is>
           <t>4500</t>
         </is>
       </c>
-      <c r="M5" s="79">
+      <c r="M5" s="76">
         <f>IF(AND(K5&lt;&gt;"",L5&lt;&gt;""),(K5+L5)/2,"")</f>
         <v/>
       </c>
-      <c r="N5" s="80" t="inlineStr">
+      <c r="N5" s="77" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="O5" s="80" t="inlineStr">
+      <c r="O5" s="77" t="inlineStr">
         <is>
           <t>203</t>
         </is>
       </c>
-      <c r="P5" s="76" t="inlineStr">
+      <c r="P5" s="78" t="inlineStr">
         <is>
           <t>mid</t>
         </is>
       </c>
-      <c r="Q5" s="77" t="inlineStr">
+      <c r="Q5" s="79" t="inlineStr">
         <is>
           <t>TAKE</t>
         </is>
@@ -1926,7 +5297,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="U5" s="79">
+      <c r="U5" s="76">
         <f>IF(AND(M5&lt;&gt;"",T5&lt;&gt;""),M5/T5,"")</f>
         <v/>
       </c>
@@ -2026,12 +5397,12 @@
           <t>326</t>
         </is>
       </c>
-      <c r="P6" s="76" t="inlineStr">
+      <c r="P6" s="78" t="inlineStr">
         <is>
           <t>mid</t>
         </is>
       </c>
-      <c r="Q6" s="77" t="inlineStr">
+      <c r="Q6" s="79" t="inlineStr">
         <is>
           <t>TAKE</t>
         </is>
@@ -2046,7 +5417,7 @@
           <t>med</t>
         </is>
       </c>
-      <c r="T6" s="78" t="inlineStr">
+      <c r="T6" s="80" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -2127,26 +5498,26 @@
           <t>Python, парсинг, данные</t>
         </is>
       </c>
-      <c r="K7" s="79" t="inlineStr">
+      <c r="K7" s="76" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="L7" s="79" t="inlineStr">
+      <c r="L7" s="76" t="inlineStr">
         <is>
           <t>30000</t>
         </is>
       </c>
-      <c r="M7" s="79">
+      <c r="M7" s="76">
         <f>IF(AND(K7&lt;&gt;"",L7&lt;&gt;""),(K7+L7)/2,"")</f>
         <v/>
       </c>
-      <c r="N7" s="80" t="inlineStr">
+      <c r="N7" s="77" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="O7" s="80" t="inlineStr">
+      <c r="O7" s="77" t="inlineStr">
         <is>
           <t>711</t>
         </is>
@@ -2156,7 +5527,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="Q7" s="77" t="inlineStr">
+      <c r="Q7" s="79" t="inlineStr">
         <is>
           <t>TAKE WITH SCOPE</t>
         </is>
@@ -2176,7 +5547,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="U7" s="79">
+      <c r="U7" s="76">
         <f>IF(AND(M7&lt;&gt;"",T7&lt;&gt;""),M7/T7,"")</f>
         <v/>
       </c>
@@ -2296,7 +5667,7 @@
           <t>med</t>
         </is>
       </c>
-      <c r="T8" s="78" t="inlineStr">
+      <c r="T8" s="80" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -2377,26 +5748,26 @@
           <t>Web, WordPress, SEO</t>
         </is>
       </c>
-      <c r="K9" s="79" t="inlineStr">
+      <c r="K9" s="76" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="L9" s="79" t="inlineStr">
+      <c r="L9" s="76" t="inlineStr">
         <is>
           <t>30000</t>
         </is>
       </c>
-      <c r="M9" s="79">
+      <c r="M9" s="76">
         <f>IF(AND(K9&lt;&gt;"",L9&lt;&gt;""),(K9+L9)/2,"")</f>
         <v/>
       </c>
-      <c r="N9" s="80" t="inlineStr">
+      <c r="N9" s="77" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="O9" s="80" t="inlineStr">
+      <c r="O9" s="77" t="inlineStr">
         <is>
           <t>659</t>
         </is>
@@ -2406,7 +5777,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="Q9" s="77" t="inlineStr">
+      <c r="Q9" s="79" t="inlineStr">
         <is>
           <t>TAKE WITH SCOPE</t>
         </is>
@@ -2426,7 +5797,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="U9" s="79">
+      <c r="U9" s="76">
         <f>IF(AND(M9&lt;&gt;"",T9&lt;&gt;""),M9/T9,"")</f>
         <v/>
       </c>
@@ -2526,12 +5897,12 @@
           <t>101</t>
         </is>
       </c>
-      <c r="P10" s="77" t="inlineStr">
+      <c r="P10" s="79" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="Q10" s="77" t="inlineStr">
+      <c r="Q10" s="79" t="inlineStr">
         <is>
           <t>TAKE FIRST</t>
         </is>
@@ -2546,7 +5917,7 @@
           <t>low</t>
         </is>
       </c>
-      <c r="T10" s="78" t="inlineStr">
+      <c r="T10" s="80" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -2627,36 +5998,36 @@
           <t>1С, учет, ОСВ, акты</t>
         </is>
       </c>
-      <c r="K11" s="79" t="inlineStr">
+      <c r="K11" s="76" t="inlineStr">
         <is>
           <t>2000</t>
         </is>
       </c>
-      <c r="L11" s="79" t="inlineStr">
+      <c r="L11" s="76" t="inlineStr">
         <is>
           <t>2000</t>
         </is>
       </c>
-      <c r="M11" s="79">
+      <c r="M11" s="76">
         <f>IF(AND(K11&lt;&gt;"",L11&lt;&gt;""),(K11+L11)/2,"")</f>
         <v/>
       </c>
-      <c r="N11" s="80" t="inlineStr">
+      <c r="N11" s="77" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="O11" s="80" t="inlineStr">
+      <c r="O11" s="77" t="inlineStr">
         <is>
           <t>245</t>
         </is>
       </c>
-      <c r="P11" s="77" t="inlineStr">
+      <c r="P11" s="79" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="Q11" s="77" t="inlineStr">
+      <c r="Q11" s="79" t="inlineStr">
         <is>
           <t>TAKE FIRST</t>
         </is>
@@ -2676,7 +6047,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="U11" s="79">
+      <c r="U11" s="76">
         <f>IF(AND(M11&lt;&gt;"",T11&lt;&gt;""),M11/T11,"")</f>
         <v/>
       </c>
@@ -2776,12 +6147,12 @@
           <t>162</t>
         </is>
       </c>
-      <c r="P12" s="76" t="inlineStr">
+      <c r="P12" s="78" t="inlineStr">
         <is>
           <t>mid</t>
         </is>
       </c>
-      <c r="Q12" s="77" t="inlineStr">
+      <c r="Q12" s="79" t="inlineStr">
         <is>
           <t>TAKE</t>
         </is>
@@ -2796,7 +6167,7 @@
           <t>low</t>
         </is>
       </c>
-      <c r="T12" s="78" t="inlineStr">
+      <c r="T12" s="80" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -2877,26 +6248,26 @@
           <t>1С, учет, ОСВ, акты</t>
         </is>
       </c>
-      <c r="K13" s="79" t="inlineStr">
+      <c r="K13" s="76" t="inlineStr">
         <is>
           <t>60000</t>
         </is>
       </c>
-      <c r="L13" s="79" t="inlineStr">
+      <c r="L13" s="76" t="inlineStr">
         <is>
           <t>180000</t>
         </is>
       </c>
-      <c r="M13" s="79">
+      <c r="M13" s="76">
         <f>IF(AND(K13&lt;&gt;"",L13&lt;&gt;""),(K13+L13)/2,"")</f>
         <v/>
       </c>
-      <c r="N13" s="80" t="inlineStr">
+      <c r="N13" s="77" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="O13" s="80" t="inlineStr">
+      <c r="O13" s="77" t="inlineStr">
         <is>
           <t>708</t>
         </is>
@@ -2906,7 +6277,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="Q13" s="77" t="inlineStr">
+      <c r="Q13" s="79" t="inlineStr">
         <is>
           <t>TAKE WITH SCOPE</t>
         </is>
@@ -2926,7 +6297,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="U13" s="79">
+      <c r="U13" s="76">
         <f>IF(AND(M13&lt;&gt;"",T13&lt;&gt;""),M13/T13,"")</f>
         <v/>
       </c>
@@ -3026,12 +6397,12 @@
           <t>284</t>
         </is>
       </c>
-      <c r="P14" s="76" t="inlineStr">
+      <c r="P14" s="78" t="inlineStr">
         <is>
           <t>mid</t>
         </is>
       </c>
-      <c r="Q14" s="77" t="inlineStr">
+      <c r="Q14" s="79" t="inlineStr">
         <is>
           <t>TAKE</t>
         </is>
@@ -3046,7 +6417,7 @@
           <t>low</t>
         </is>
       </c>
-      <c r="T14" s="78" t="inlineStr">
+      <c r="T14" s="80" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -3127,36 +6498,36 @@
           <t>Маркетинговая аналитика</t>
         </is>
       </c>
-      <c r="K15" s="79" t="inlineStr">
+      <c r="K15" s="76" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="L15" s="79" t="inlineStr">
+      <c r="L15" s="76" t="inlineStr">
         <is>
           <t>30000</t>
         </is>
       </c>
-      <c r="M15" s="79">
+      <c r="M15" s="76">
         <f>IF(AND(K15&lt;&gt;"",L15&lt;&gt;""),(K15+L15)/2,"")</f>
         <v/>
       </c>
-      <c r="N15" s="80" t="inlineStr">
+      <c r="N15" s="77" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="O15" s="80" t="inlineStr">
+      <c r="O15" s="77" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="P15" s="76" t="inlineStr">
+      <c r="P15" s="78" t="inlineStr">
         <is>
           <t>mid</t>
         </is>
       </c>
-      <c r="Q15" s="77" t="inlineStr">
+      <c r="Q15" s="79" t="inlineStr">
         <is>
           <t>TAKE</t>
         </is>
@@ -3176,7 +6547,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="U15" s="79">
+      <c r="U15" s="76">
         <f>IF(AND(M15&lt;&gt;"",T15&lt;&gt;""),M15/T15,"")</f>
         <v/>
       </c>
@@ -3281,7 +6652,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="Q16" s="77" t="inlineStr">
+      <c r="Q16" s="79" t="inlineStr">
         <is>
           <t>TAKE WITH SCOPE</t>
         </is>
@@ -3296,7 +6667,7 @@
           <t>low</t>
         </is>
       </c>
-      <c r="T16" s="78" t="inlineStr">
+      <c r="T16" s="80" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -3377,26 +6748,26 @@
           <t>Маркетплейсы</t>
         </is>
       </c>
-      <c r="K17" s="79" t="inlineStr">
+      <c r="K17" s="76" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="L17" s="79" t="inlineStr">
+      <c r="L17" s="76" t="inlineStr">
         <is>
           <t>30000</t>
         </is>
       </c>
-      <c r="M17" s="79">
+      <c r="M17" s="76">
         <f>IF(AND(K17&lt;&gt;"",L17&lt;&gt;""),(K17+L17)/2,"")</f>
         <v/>
       </c>
-      <c r="N17" s="80" t="inlineStr">
+      <c r="N17" s="77" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="O17" s="80" t="inlineStr">
+      <c r="O17" s="77" t="inlineStr">
         <is>
           <t>579</t>
         </is>
@@ -3406,7 +6777,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="Q17" s="77" t="inlineStr">
+      <c r="Q17" s="79" t="inlineStr">
         <is>
           <t>TAKE WITH SCOPE</t>
         </is>
@@ -3426,7 +6797,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="U17" s="79">
+      <c r="U17" s="76">
         <f>IF(AND(M17&lt;&gt;"",T17&lt;&gt;""),M17/T17,"")</f>
         <v/>
       </c>
@@ -3531,7 +6902,7 @@
           <t>red</t>
         </is>
       </c>
-      <c r="Q18" s="77" t="inlineStr">
+      <c r="Q18" s="79" t="inlineStr">
         <is>
           <t>TAKE ONLY if bounded and proof useful</t>
         </is>
@@ -3546,7 +6917,7 @@
           <t>med</t>
         </is>
       </c>
-      <c r="T18" s="78" t="str"/>
+      <c r="T18" s="80" t="str"/>
       <c r="U18" s="74">
         <f>IF(AND(M18&lt;&gt;"",T18&lt;&gt;""),M18/T18,"")</f>
         <v/>
@@ -3623,26 +6994,26 @@
           <t>Маркетплейсы</t>
         </is>
       </c>
-      <c r="K19" s="79" t="inlineStr">
+      <c r="K19" s="76" t="inlineStr">
         <is>
           <t>2000</t>
         </is>
       </c>
-      <c r="L19" s="79" t="inlineStr">
+      <c r="L19" s="76" t="inlineStr">
         <is>
           <t>6000</t>
         </is>
       </c>
-      <c r="M19" s="79">
+      <c r="M19" s="76">
         <f>IF(AND(K19&lt;&gt;"",L19&lt;&gt;""),(K19+L19)/2,"")</f>
         <v/>
       </c>
-      <c r="N19" s="80" t="inlineStr">
+      <c r="N19" s="77" t="inlineStr">
         <is>
           <t>125</t>
         </is>
       </c>
-      <c r="O19" s="80" t="inlineStr">
+      <c r="O19" s="77" t="inlineStr">
         <is>
           <t>838</t>
         </is>
@@ -3652,7 +7023,7 @@
           <t>red</t>
         </is>
       </c>
-      <c r="Q19" s="77" t="inlineStr">
+      <c r="Q19" s="79" t="inlineStr">
         <is>
           <t>TAKE ONLY if bounded and proof useful</t>
         </is>
@@ -3668,7 +7039,7 @@
         </is>
       </c>
       <c r="T19" s="82" t="str"/>
-      <c r="U19" s="79">
+      <c r="U19" s="76">
         <f>IF(AND(M19&lt;&gt;"",T19&lt;&gt;""),M19/T19,"")</f>
         <v/>
       </c>
@@ -3768,7 +7139,7 @@
           <t>632</t>
         </is>
       </c>
-      <c r="P20" s="77" t="inlineStr">
+      <c r="P20" s="79" t="inlineStr">
         <is>
           <t>low</t>
         </is>
@@ -3788,7 +7159,7 @@
           <t>low</t>
         </is>
       </c>
-      <c r="T20" s="78" t="inlineStr">
+      <c r="T20" s="80" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -3869,36 +7240,36 @@
           <t>AI, боты, CRM</t>
         </is>
       </c>
-      <c r="K21" s="79" t="inlineStr">
+      <c r="K21" s="76" t="inlineStr">
         <is>
           <t>25000</t>
         </is>
       </c>
-      <c r="L21" s="79" t="inlineStr">
+      <c r="L21" s="76" t="inlineStr">
         <is>
           <t>75000</t>
         </is>
       </c>
-      <c r="M21" s="79">
+      <c r="M21" s="76">
         <f>IF(AND(K21&lt;&gt;"",L21&lt;&gt;""),(K21+L21)/2,"")</f>
         <v/>
       </c>
-      <c r="N21" s="80" t="inlineStr">
+      <c r="N21" s="77" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="O21" s="80" t="inlineStr">
+      <c r="O21" s="77" t="inlineStr">
         <is>
           <t>181</t>
         </is>
       </c>
-      <c r="P21" s="77" t="inlineStr">
+      <c r="P21" s="79" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="Q21" s="77" t="inlineStr">
+      <c r="Q21" s="79" t="inlineStr">
         <is>
           <t>TAKE FIRST</t>
         </is>
@@ -3918,7 +7289,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="U21" s="79">
+      <c r="U21" s="76">
         <f>IF(AND(M21&lt;&gt;"",T21&lt;&gt;""),M21/T21,"")</f>
         <v/>
       </c>
@@ -4018,7 +7389,7 @@
           <t>638</t>
         </is>
       </c>
-      <c r="P22" s="76" t="inlineStr">
+      <c r="P22" s="78" t="inlineStr">
         <is>
           <t>mid</t>
         </is>
@@ -4038,7 +7409,7 @@
           <t>med</t>
         </is>
       </c>
-      <c r="T22" s="78" t="inlineStr">
+      <c r="T22" s="80" t="inlineStr">
         <is>
           <t>24</t>
         </is>
@@ -4119,26 +7490,26 @@
           <t>AI, боты, CRM</t>
         </is>
       </c>
-      <c r="K23" s="79" t="inlineStr">
+      <c r="K23" s="76" t="inlineStr">
         <is>
           <t>5000</t>
         </is>
       </c>
-      <c r="L23" s="79" t="inlineStr">
+      <c r="L23" s="76" t="inlineStr">
         <is>
           <t>15000</t>
         </is>
       </c>
-      <c r="M23" s="79">
+      <c r="M23" s="76">
         <f>IF(AND(K23&lt;&gt;"",L23&lt;&gt;""),(K23+L23)/2,"")</f>
         <v/>
       </c>
-      <c r="N23" s="80" t="inlineStr">
+      <c r="N23" s="77" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="O23" s="80" t="inlineStr">
+      <c r="O23" s="77" t="inlineStr">
         <is>
           <t>454</t>
         </is>
@@ -4148,7 +7519,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="Q23" s="77" t="inlineStr">
+      <c r="Q23" s="79" t="inlineStr">
         <is>
           <t>TAKE WITH SCOPE</t>
         </is>
@@ -4168,7 +7539,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="U23" s="79">
+      <c r="U23" s="76">
         <f>IF(AND(M23&lt;&gt;"",T23&lt;&gt;""),M23/T23,"")</f>
         <v/>
       </c>
@@ -4288,7 +7659,7 @@
           <t>med</t>
         </is>
       </c>
-      <c r="T24" s="78" t="inlineStr">
+      <c r="T24" s="80" t="inlineStr">
         <is>
           <t>24</t>
         </is>
@@ -4369,26 +7740,26 @@
           <t>AI, боты, CRM</t>
         </is>
       </c>
-      <c r="K25" s="79" t="inlineStr">
+      <c r="K25" s="76" t="inlineStr">
         <is>
           <t>6500</t>
         </is>
       </c>
-      <c r="L25" s="79" t="inlineStr">
+      <c r="L25" s="76" t="inlineStr">
         <is>
           <t>19500</t>
         </is>
       </c>
-      <c r="M25" s="79">
+      <c r="M25" s="76">
         <f>IF(AND(K25&lt;&gt;"",L25&lt;&gt;""),(K25+L25)/2,"")</f>
         <v/>
       </c>
-      <c r="N25" s="80" t="inlineStr">
+      <c r="N25" s="77" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="O25" s="80" t="inlineStr">
+      <c r="O25" s="77" t="inlineStr">
         <is>
           <t>605</t>
         </is>
@@ -4398,7 +7769,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="Q25" s="77" t="inlineStr">
+      <c r="Q25" s="79" t="inlineStr">
         <is>
           <t>TAKE WITH SCOPE</t>
         </is>
@@ -4418,7 +7789,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="U25" s="79">
+      <c r="U25" s="76">
         <f>IF(AND(M25&lt;&gt;"",T25&lt;&gt;""),M25/T25,"")</f>
         <v/>
       </c>
@@ -4538,7 +7909,7 @@
           <t>med</t>
         </is>
       </c>
-      <c r="T26" s="78" t="inlineStr">
+      <c r="T26" s="80" t="inlineStr">
         <is>
           <t>24</t>
         </is>
@@ -4619,26 +7990,26 @@
           <t>AI, боты, CRM</t>
         </is>
       </c>
-      <c r="K27" s="79" t="inlineStr">
+      <c r="K27" s="76" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="L27" s="79" t="inlineStr">
+      <c r="L27" s="76" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="M27" s="79">
+      <c r="M27" s="76">
         <f>IF(AND(K27&lt;&gt;"",L27&lt;&gt;""),(K27+L27)/2,"")</f>
         <v/>
       </c>
-      <c r="N27" s="80" t="inlineStr">
+      <c r="N27" s="77" t="inlineStr">
         <is>
           <t>87</t>
         </is>
       </c>
-      <c r="O27" s="80" t="inlineStr">
+      <c r="O27" s="77" t="inlineStr">
         <is>
           <t>1053</t>
         </is>
@@ -4668,7 +8039,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="U27" s="79">
+      <c r="U27" s="76">
         <f>IF(AND(M27&lt;&gt;"",T27&lt;&gt;""),M27/T27,"")</f>
         <v/>
       </c>
@@ -4788,7 +8159,7 @@
           <t>med</t>
         </is>
       </c>
-      <c r="T28" s="78" t="inlineStr">
+      <c r="T28" s="80" t="inlineStr">
         <is>
           <t>24</t>
         </is>
@@ -4869,36 +8240,36 @@
           <t>B2B, КП, лиды</t>
         </is>
       </c>
-      <c r="K29" s="79" t="inlineStr">
+      <c r="K29" s="76" t="inlineStr">
         <is>
           <t>25000</t>
         </is>
       </c>
-      <c r="L29" s="79" t="inlineStr">
+      <c r="L29" s="76" t="inlineStr">
         <is>
           <t>75000</t>
         </is>
       </c>
-      <c r="M29" s="79">
+      <c r="M29" s="76">
         <f>IF(AND(K29&lt;&gt;"",L29&lt;&gt;""),(K29+L29)/2,"")</f>
         <v/>
       </c>
-      <c r="N29" s="80" t="inlineStr">
+      <c r="N29" s="77" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O29" s="80" t="inlineStr">
+      <c r="O29" s="77" t="inlineStr">
         <is>
           <t>128</t>
         </is>
       </c>
-      <c r="P29" s="77" t="inlineStr">
+      <c r="P29" s="79" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="Q29" s="77" t="inlineStr">
+      <c r="Q29" s="79" t="inlineStr">
         <is>
           <t>TAKE FIRST</t>
         </is>
@@ -4918,7 +8289,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="U29" s="79">
+      <c r="U29" s="76">
         <f>IF(AND(M29&lt;&gt;"",T29&lt;&gt;""),M29/T29,"")</f>
         <v/>
       </c>
@@ -5018,12 +8389,12 @@
           <t>573</t>
         </is>
       </c>
-      <c r="P30" s="77" t="inlineStr">
+      <c r="P30" s="79" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="Q30" s="77" t="inlineStr">
+      <c r="Q30" s="79" t="inlineStr">
         <is>
           <t>TAKE FIRST</t>
         </is>
@@ -5038,7 +8409,7 @@
           <t>low</t>
         </is>
       </c>
-      <c r="T30" s="78" t="inlineStr">
+      <c r="T30" s="80" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -5119,36 +8490,36 @@
           <t>B2B, КП, лиды</t>
         </is>
       </c>
-      <c r="K31" s="79" t="inlineStr">
+      <c r="K31" s="76" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="L31" s="79" t="inlineStr">
+      <c r="L31" s="76" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="M31" s="79">
+      <c r="M31" s="76">
         <f>IF(AND(K31&lt;&gt;"",L31&lt;&gt;""),(K31+L31)/2,"")</f>
         <v/>
       </c>
-      <c r="N31" s="80" t="inlineStr">
+      <c r="N31" s="77" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="O31" s="80" t="inlineStr">
+      <c r="O31" s="77" t="inlineStr">
         <is>
           <t>493</t>
         </is>
       </c>
-      <c r="P31" s="77" t="inlineStr">
+      <c r="P31" s="79" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="Q31" s="77" t="inlineStr">
+      <c r="Q31" s="79" t="inlineStr">
         <is>
           <t>TAKE FIRST</t>
         </is>
@@ -5168,7 +8539,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="U31" s="79">
+      <c r="U31" s="76">
         <f>IF(AND(M31&lt;&gt;"",T31&lt;&gt;""),M31/T31,"")</f>
         <v/>
       </c>
@@ -5268,12 +8639,12 @@
           <t>227</t>
         </is>
       </c>
-      <c r="P32" s="77" t="inlineStr">
+      <c r="P32" s="79" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="Q32" s="77" t="inlineStr">
+      <c r="Q32" s="79" t="inlineStr">
         <is>
           <t>TAKE FIRST</t>
         </is>
@@ -5288,7 +8659,7 @@
           <t>low</t>
         </is>
       </c>
-      <c r="T32" s="78" t="inlineStr">
+      <c r="T32" s="80" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -5369,36 +8740,36 @@
           <t>B2B, КП, лиды</t>
         </is>
       </c>
-      <c r="K33" s="79" t="inlineStr">
+      <c r="K33" s="76" t="inlineStr">
         <is>
           <t>30000</t>
         </is>
       </c>
-      <c r="L33" s="79" t="inlineStr">
+      <c r="L33" s="76" t="inlineStr">
         <is>
           <t>90000</t>
         </is>
       </c>
-      <c r="M33" s="79">
+      <c r="M33" s="76">
         <f>IF(AND(K33&lt;&gt;"",L33&lt;&gt;""),(K33+L33)/2,"")</f>
         <v/>
       </c>
-      <c r="N33" s="80" t="inlineStr">
+      <c r="N33" s="77" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O33" s="80" t="inlineStr">
+      <c r="O33" s="77" t="inlineStr">
         <is>
           <t>1136</t>
         </is>
       </c>
-      <c r="P33" s="77" t="inlineStr">
+      <c r="P33" s="79" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="Q33" s="77" t="inlineStr">
+      <c r="Q33" s="79" t="inlineStr">
         <is>
           <t>TAKE FIRST</t>
         </is>
@@ -5418,7 +8789,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="U33" s="79">
+      <c r="U33" s="76">
         <f>IF(AND(M33&lt;&gt;"",T33&lt;&gt;""),M33/T33,"")</f>
         <v/>
       </c>
@@ -5518,12 +8889,12 @@
           <t>301</t>
         </is>
       </c>
-      <c r="P34" s="76" t="inlineStr">
+      <c r="P34" s="78" t="inlineStr">
         <is>
           <t>mid</t>
         </is>
       </c>
-      <c r="Q34" s="77" t="inlineStr">
+      <c r="Q34" s="79" t="inlineStr">
         <is>
           <t>TAKE</t>
         </is>
@@ -5538,7 +8909,7 @@
           <t>low</t>
         </is>
       </c>
-      <c r="T34" s="78" t="inlineStr">
+      <c r="T34" s="80" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -5619,26 +8990,26 @@
           <t>Excel и таблицы</t>
         </is>
       </c>
-      <c r="K35" s="79" t="inlineStr">
+      <c r="K35" s="76" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="L35" s="79" t="inlineStr">
+      <c r="L35" s="76" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
       </c>
-      <c r="M35" s="79">
+      <c r="M35" s="76">
         <f>IF(AND(K35&lt;&gt;"",L35&lt;&gt;""),(K35+L35)/2,"")</f>
         <v/>
       </c>
-      <c r="N35" s="80" t="inlineStr">
+      <c r="N35" s="77" t="inlineStr">
         <is>
           <t>121</t>
         </is>
       </c>
-      <c r="O35" s="80" t="inlineStr">
+      <c r="O35" s="77" t="inlineStr">
         <is>
           <t>997</t>
         </is>
@@ -5664,7 +9035,7 @@
         </is>
       </c>
       <c r="T35" s="82" t="str"/>
-      <c r="U35" s="79">
+      <c r="U35" s="76">
         <f>IF(AND(M35&lt;&gt;"",T35&lt;&gt;""),M35/T35,"")</f>
         <v/>
       </c>
@@ -5784,7 +9155,7 @@
           <t>med</t>
         </is>
       </c>
-      <c r="T36" s="78" t="str"/>
+      <c r="T36" s="80" t="str"/>
       <c r="U36" s="74">
         <f>IF(AND(M36&lt;&gt;"",T36&lt;&gt;""),M36/T36,"")</f>
         <v/>
@@ -5861,36 +9232,36 @@
           <t>Python, парсинг, данные</t>
         </is>
       </c>
-      <c r="K37" s="79" t="inlineStr">
+      <c r="K37" s="76" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="L37" s="79" t="inlineStr">
+      <c r="L37" s="76" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="M37" s="79">
+      <c r="M37" s="76">
         <f>IF(AND(K37&lt;&gt;"",L37&lt;&gt;""),(K37+L37)/2,"")</f>
         <v/>
       </c>
-      <c r="N37" s="80" t="inlineStr">
+      <c r="N37" s="77" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="O37" s="80" t="inlineStr">
+      <c r="O37" s="77" t="inlineStr">
         <is>
           <t>313</t>
         </is>
       </c>
-      <c r="P37" s="76" t="inlineStr">
+      <c r="P37" s="78" t="inlineStr">
         <is>
           <t>mid</t>
         </is>
       </c>
-      <c r="Q37" s="77" t="inlineStr">
+      <c r="Q37" s="79" t="inlineStr">
         <is>
           <t>TAKE</t>
         </is>
@@ -5910,7 +9281,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="U37" s="79">
+      <c r="U37" s="76">
         <f>IF(AND(M37&lt;&gt;"",T37&lt;&gt;""),M37/T37,"")</f>
         <v/>
       </c>
@@ -6010,12 +9381,12 @@
           <t>184</t>
         </is>
       </c>
-      <c r="P38" s="76" t="inlineStr">
+      <c r="P38" s="78" t="inlineStr">
         <is>
           <t>mid</t>
         </is>
       </c>
-      <c r="Q38" s="77" t="inlineStr">
+      <c r="Q38" s="79" t="inlineStr">
         <is>
           <t>TAKE</t>
         </is>
@@ -6030,7 +9401,7 @@
           <t>low</t>
         </is>
       </c>
-      <c r="T38" s="78" t="inlineStr">
+      <c r="T38" s="80" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -6111,36 +9482,36 @@
           <t>Python, парсинг, данные</t>
         </is>
       </c>
-      <c r="K39" s="79" t="inlineStr">
+      <c r="K39" s="76" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="L39" s="79" t="inlineStr">
+      <c r="L39" s="76" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="M39" s="79">
+      <c r="M39" s="76">
         <f>IF(AND(K39&lt;&gt;"",L39&lt;&gt;""),(K39+L39)/2,"")</f>
         <v/>
       </c>
-      <c r="N39" s="80" t="inlineStr">
+      <c r="N39" s="77" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="O39" s="80" t="inlineStr">
+      <c r="O39" s="77" t="inlineStr">
         <is>
           <t>355</t>
         </is>
       </c>
-      <c r="P39" s="76" t="inlineStr">
+      <c r="P39" s="78" t="inlineStr">
         <is>
           <t>mid</t>
         </is>
       </c>
-      <c r="Q39" s="77" t="inlineStr">
+      <c r="Q39" s="79" t="inlineStr">
         <is>
           <t>TAKE</t>
         </is>
@@ -6160,7 +9531,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="U39" s="79">
+      <c r="U39" s="76">
         <f>IF(AND(M39&lt;&gt;"",T39&lt;&gt;""),M39/T39,"")</f>
         <v/>
       </c>
@@ -6265,7 +9636,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="Q40" s="77" t="inlineStr">
+      <c r="Q40" s="79" t="inlineStr">
         <is>
           <t>TAKE WITH SCOPE</t>
         </is>
@@ -6280,7 +9651,7 @@
           <t>low</t>
         </is>
       </c>
-      <c r="T40" s="78" t="inlineStr">
+      <c r="T40" s="80" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -6361,26 +9732,26 @@
           <t>Python, парсинг, данные</t>
         </is>
       </c>
-      <c r="K41" s="79" t="inlineStr">
+      <c r="K41" s="76" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="L41" s="79" t="inlineStr">
+      <c r="L41" s="76" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
       </c>
-      <c r="M41" s="79">
+      <c r="M41" s="76">
         <f>IF(AND(K41&lt;&gt;"",L41&lt;&gt;""),(K41+L41)/2,"")</f>
         <v/>
       </c>
-      <c r="N41" s="80" t="inlineStr">
+      <c r="N41" s="77" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="O41" s="80" t="inlineStr">
+      <c r="O41" s="77" t="inlineStr">
         <is>
           <t>619</t>
         </is>
@@ -6390,7 +9761,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="Q41" s="77" t="inlineStr">
+      <c r="Q41" s="79" t="inlineStr">
         <is>
           <t>TAKE WITH SCOPE</t>
         </is>
@@ -6410,7 +9781,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="U41" s="79">
+      <c r="U41" s="76">
         <f>IF(AND(M41&lt;&gt;"",T41&lt;&gt;""),M41/T41,"")</f>
         <v/>
       </c>
@@ -6515,7 +9886,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="Q42" s="77" t="inlineStr">
+      <c r="Q42" s="79" t="inlineStr">
         <is>
           <t>TAKE WITH SCOPE</t>
         </is>
@@ -6530,7 +9901,7 @@
           <t>low</t>
         </is>
       </c>
-      <c r="T42" s="78" t="inlineStr">
+      <c r="T42" s="80" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -6611,36 +9982,36 @@
           <t>Python, парсинг, данные</t>
         </is>
       </c>
-      <c r="K43" s="79" t="inlineStr">
+      <c r="K43" s="76" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
       </c>
-      <c r="L43" s="79" t="inlineStr">
+      <c r="L43" s="76" t="inlineStr">
         <is>
           <t>9000</t>
         </is>
       </c>
-      <c r="M43" s="79">
+      <c r="M43" s="76">
         <f>IF(AND(K43&lt;&gt;"",L43&lt;&gt;""),(K43+L43)/2,"")</f>
         <v/>
       </c>
-      <c r="N43" s="80" t="inlineStr">
+      <c r="N43" s="77" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O43" s="80" t="inlineStr">
+      <c r="O43" s="77" t="inlineStr">
         <is>
           <t>91</t>
         </is>
       </c>
-      <c r="P43" s="77" t="inlineStr">
+      <c r="P43" s="79" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="Q43" s="77" t="inlineStr">
+      <c r="Q43" s="79" t="inlineStr">
         <is>
           <t>TAKE FIRST</t>
         </is>
@@ -6660,7 +10031,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="U43" s="79">
+      <c r="U43" s="76">
         <f>IF(AND(M43&lt;&gt;"",T43&lt;&gt;""),M43/T43,"")</f>
         <v/>
       </c>
@@ -6760,12 +10131,12 @@
           <t>1040</t>
         </is>
       </c>
-      <c r="P44" s="77" t="inlineStr">
+      <c r="P44" s="79" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="Q44" s="77" t="inlineStr">
+      <c r="Q44" s="79" t="inlineStr">
         <is>
           <t>TAKE FIRST</t>
         </is>
@@ -6780,7 +10151,7 @@
           <t>low</t>
         </is>
       </c>
-      <c r="T44" s="78" t="inlineStr">
+      <c r="T44" s="80" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -6861,26 +10232,26 @@
           <t>Web, WordPress, SEO</t>
         </is>
       </c>
-      <c r="K45" s="79" t="inlineStr">
+      <c r="K45" s="76" t="inlineStr">
         <is>
           <t>15000</t>
         </is>
       </c>
-      <c r="L45" s="79" t="inlineStr">
+      <c r="L45" s="76" t="inlineStr">
         <is>
           <t>45000</t>
         </is>
       </c>
-      <c r="M45" s="79">
+      <c r="M45" s="76">
         <f>IF(AND(K45&lt;&gt;"",L45&lt;&gt;""),(K45+L45)/2,"")</f>
         <v/>
       </c>
-      <c r="N45" s="80" t="inlineStr">
+      <c r="N45" s="77" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O45" s="80" t="inlineStr">
+      <c r="O45" s="77" t="inlineStr">
         <is>
           <t>193</t>
         </is>
@@ -6890,7 +10261,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="Q45" s="77" t="inlineStr">
+      <c r="Q45" s="79" t="inlineStr">
         <is>
           <t>TAKE WITH SCOPE</t>
         </is>
@@ -6910,7 +10281,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="U45" s="79">
+      <c r="U45" s="76">
         <f>IF(AND(M45&lt;&gt;"",T45&lt;&gt;""),M45/T45,"")</f>
         <v/>
       </c>
@@ -7030,7 +10401,7 @@
           <t>low</t>
         </is>
       </c>
-      <c r="T46" s="78" t="inlineStr">
+      <c r="T46" s="80" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -7111,27 +10482,27 @@
           <t>1С, учет, ОСВ, акты</t>
         </is>
       </c>
-      <c r="K47" s="79" t="inlineStr">
+      <c r="K47" s="76" t="inlineStr">
         <is>
           <t>30000</t>
         </is>
       </c>
-      <c r="L47" s="79" t="inlineStr">
+      <c r="L47" s="76" t="inlineStr">
         <is>
           <t>30000</t>
         </is>
       </c>
-      <c r="M47" s="79">
+      <c r="M47" s="76">
         <f>IF(AND(K47&lt;&gt;"",L47&lt;&gt;""),(K47+L47)/2,"")</f>
         <v/>
       </c>
-      <c r="N47" s="80" t="inlineStr">
+      <c r="N47" s="77" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O47" s="80" t="str"/>
-      <c r="P47" s="77" t="inlineStr">
+      <c r="O47" s="77" t="str"/>
+      <c r="P47" s="79" t="inlineStr">
         <is>
           <t>low</t>
         </is>
@@ -7156,7 +10527,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="U47" s="79">
+      <c r="U47" s="76">
         <f>IF(AND(M47&lt;&gt;"",T47&lt;&gt;""),M47/T47,"")</f>
         <v/>
       </c>
@@ -7252,7 +10623,7 @@
         </is>
       </c>
       <c r="O48" s="75" t="str"/>
-      <c r="P48" s="77" t="inlineStr">
+      <c r="P48" s="79" t="inlineStr">
         <is>
           <t>low</t>
         </is>
@@ -7272,7 +10643,7 @@
           <t>med</t>
         </is>
       </c>
-      <c r="T48" s="78" t="inlineStr">
+      <c r="T48" s="80" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -7353,32 +10724,32 @@
           <t>Документы, договоры, заявки</t>
         </is>
       </c>
-      <c r="K49" s="79" t="inlineStr">
+      <c r="K49" s="76" t="inlineStr">
         <is>
           <t>9000</t>
         </is>
       </c>
-      <c r="L49" s="79" t="inlineStr">
+      <c r="L49" s="76" t="inlineStr">
         <is>
           <t>9000</t>
         </is>
       </c>
-      <c r="M49" s="79">
+      <c r="M49" s="76">
         <f>IF(AND(K49&lt;&gt;"",L49&lt;&gt;""),(K49+L49)/2,"")</f>
         <v/>
       </c>
-      <c r="N49" s="80" t="inlineStr">
+      <c r="N49" s="77" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O49" s="80" t="str"/>
-      <c r="P49" s="77" t="inlineStr">
+      <c r="O49" s="77" t="str"/>
+      <c r="P49" s="79" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="Q49" s="77" t="inlineStr">
+      <c r="Q49" s="79" t="inlineStr">
         <is>
           <t>TAKE</t>
         </is>
@@ -7398,7 +10769,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="U49" s="79">
+      <c r="U49" s="76">
         <f>IF(AND(M49&lt;&gt;"",T49&lt;&gt;""),M49/T49,"")</f>
         <v/>
       </c>
@@ -7494,12 +10865,12 @@
         </is>
       </c>
       <c r="O50" s="75" t="str"/>
-      <c r="P50" s="77" t="inlineStr">
+      <c r="P50" s="79" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="Q50" s="77" t="inlineStr">
+      <c r="Q50" s="79" t="inlineStr">
         <is>
           <t>TAKE_WITH_BOUNDARY</t>
         </is>
@@ -7514,7 +10885,7 @@
           <t>med</t>
         </is>
       </c>
-      <c r="T50" s="78" t="inlineStr">
+      <c r="T50" s="80" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -7595,32 +10966,32 @@
           <t>Документы, договоры, заявки</t>
         </is>
       </c>
-      <c r="K51" s="79" t="inlineStr">
+      <c r="K51" s="76" t="inlineStr">
         <is>
           <t>9000</t>
         </is>
       </c>
-      <c r="L51" s="79" t="inlineStr">
+      <c r="L51" s="76" t="inlineStr">
         <is>
           <t>9000</t>
         </is>
       </c>
-      <c r="M51" s="79">
+      <c r="M51" s="76">
         <f>IF(AND(K51&lt;&gt;"",L51&lt;&gt;""),(K51+L51)/2,"")</f>
         <v/>
       </c>
-      <c r="N51" s="80" t="inlineStr">
+      <c r="N51" s="77" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O51" s="80" t="str"/>
-      <c r="P51" s="77" t="inlineStr">
+      <c r="O51" s="77" t="str"/>
+      <c r="P51" s="79" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="Q51" s="77" t="inlineStr">
+      <c r="Q51" s="79" t="inlineStr">
         <is>
           <t>TAKE</t>
         </is>
@@ -7640,7 +11011,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="U51" s="79">
+      <c r="U51" s="76">
         <f>IF(AND(M51&lt;&gt;"",T51&lt;&gt;""),M51/T51,"")</f>
         <v/>
       </c>
@@ -7736,12 +11107,12 @@
         </is>
       </c>
       <c r="O52" s="75" t="str"/>
-      <c r="P52" s="77" t="inlineStr">
+      <c r="P52" s="79" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="Q52" s="77" t="inlineStr">
+      <c r="Q52" s="79" t="inlineStr">
         <is>
           <t>TAKE</t>
         </is>
@@ -7756,7 +11127,7 @@
           <t>low</t>
         </is>
       </c>
-      <c r="T52" s="78" t="inlineStr">
+      <c r="T52" s="80" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -7837,32 +11208,32 @@
           <t>Документы, договоры, заявки</t>
         </is>
       </c>
-      <c r="K53" s="79" t="inlineStr">
+      <c r="K53" s="76" t="inlineStr">
         <is>
           <t>5000</t>
         </is>
       </c>
-      <c r="L53" s="79" t="inlineStr">
+      <c r="L53" s="76" t="inlineStr">
         <is>
           <t>5000</t>
         </is>
       </c>
-      <c r="M53" s="79">
+      <c r="M53" s="76">
         <f>IF(AND(K53&lt;&gt;"",L53&lt;&gt;""),(K53+L53)/2,"")</f>
         <v/>
       </c>
-      <c r="N53" s="80" t="inlineStr">
+      <c r="N53" s="77" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="O53" s="80" t="str"/>
-      <c r="P53" s="76" t="inlineStr">
+      <c r="O53" s="77" t="str"/>
+      <c r="P53" s="78" t="inlineStr">
         <is>
           <t>mid</t>
         </is>
       </c>
-      <c r="Q53" s="77" t="inlineStr">
+      <c r="Q53" s="79" t="inlineStr">
         <is>
           <t>TAKE_WITH_BOUNDARY</t>
         </is>
@@ -7882,7 +11253,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="U53" s="79">
+      <c r="U53" s="76">
         <f>IF(AND(M53&lt;&gt;"",T53&lt;&gt;""),M53/T53,"")</f>
         <v/>
       </c>
@@ -7978,12 +11349,12 @@
         </is>
       </c>
       <c r="O54" s="75" t="str"/>
-      <c r="P54" s="77" t="inlineStr">
+      <c r="P54" s="79" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="Q54" s="77" t="inlineStr">
+      <c r="Q54" s="79" t="inlineStr">
         <is>
           <t>TAKE</t>
         </is>
@@ -7998,7 +11369,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="T54" s="78" t="inlineStr">
+      <c r="T54" s="80" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -8079,32 +11450,32 @@
           <t>Смешанные бизнес-задачи</t>
         </is>
       </c>
-      <c r="K55" s="79" t="inlineStr">
+      <c r="K55" s="76" t="inlineStr">
         <is>
           <t>30000</t>
         </is>
       </c>
-      <c r="L55" s="79" t="inlineStr">
+      <c r="L55" s="76" t="inlineStr">
         <is>
           <t>30000</t>
         </is>
       </c>
-      <c r="M55" s="79">
+      <c r="M55" s="76">
         <f>IF(AND(K55&lt;&gt;"",L55&lt;&gt;""),(K55+L55)/2,"")</f>
         <v/>
       </c>
-      <c r="N55" s="80" t="inlineStr">
+      <c r="N55" s="77" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O55" s="80" t="str"/>
-      <c r="P55" s="77" t="inlineStr">
+      <c r="O55" s="77" t="str"/>
+      <c r="P55" s="79" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="Q55" s="77" t="inlineStr">
+      <c r="Q55" s="79" t="inlineStr">
         <is>
           <t>TAKE_AS_POSITIONING</t>
         </is>
@@ -8124,7 +11495,7 @@
           <t>14</t>
         </is>
       </c>
-      <c r="U55" s="79">
+      <c r="U55" s="76">
         <f>IF(AND(M55&lt;&gt;"",T55&lt;&gt;""),M55/T55,"")</f>
         <v/>
       </c>
@@ -8220,7 +11591,7 @@
         </is>
       </c>
       <c r="O56" s="75" t="str"/>
-      <c r="P56" s="77" t="inlineStr">
+      <c r="P56" s="79" t="inlineStr">
         <is>
           <t>low</t>
         </is>
@@ -8240,7 +11611,7 @@
           <t>med</t>
         </is>
       </c>
-      <c r="T56" s="78" t="inlineStr">
+      <c r="T56" s="80" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -8321,27 +11692,27 @@
           <t>Смешанные бизнес-задачи</t>
         </is>
       </c>
-      <c r="K57" s="79" t="inlineStr">
+      <c r="K57" s="76" t="inlineStr">
         <is>
           <t>30000</t>
         </is>
       </c>
-      <c r="L57" s="79" t="inlineStr">
+      <c r="L57" s="76" t="inlineStr">
         <is>
           <t>30000</t>
         </is>
       </c>
-      <c r="M57" s="79">
+      <c r="M57" s="76">
         <f>IF(AND(K57&lt;&gt;"",L57&lt;&gt;""),(K57+L57)/2,"")</f>
         <v/>
       </c>
-      <c r="N57" s="80" t="inlineStr">
+      <c r="N57" s="77" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O57" s="80" t="str"/>
-      <c r="P57" s="77" t="inlineStr">
+      <c r="O57" s="77" t="str"/>
+      <c r="P57" s="79" t="inlineStr">
         <is>
           <t>low</t>
         </is>
@@ -8366,7 +11737,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="U57" s="79">
+      <c r="U57" s="76">
         <f>IF(AND(M57&lt;&gt;"",T57&lt;&gt;""),M57/T57,"")</f>
         <v/>
       </c>
@@ -8462,7 +11833,7 @@
         </is>
       </c>
       <c r="O58" s="75" t="str"/>
-      <c r="P58" s="77" t="inlineStr">
+      <c r="P58" s="79" t="inlineStr">
         <is>
           <t>low</t>
         </is>
@@ -8482,7 +11853,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="T58" s="78" t="inlineStr">
+      <c r="T58" s="80" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -8563,27 +11934,27 @@
           <t>Смешанные бизнес-задачи</t>
         </is>
       </c>
-      <c r="K59" s="79" t="inlineStr">
+      <c r="K59" s="76" t="inlineStr">
         <is>
           <t>75000</t>
         </is>
       </c>
-      <c r="L59" s="79" t="inlineStr">
+      <c r="L59" s="76" t="inlineStr">
         <is>
           <t>75000</t>
         </is>
       </c>
-      <c r="M59" s="79">
+      <c r="M59" s="76">
         <f>IF(AND(K59&lt;&gt;"",L59&lt;&gt;""),(K59+L59)/2,"")</f>
         <v/>
       </c>
-      <c r="N59" s="80" t="inlineStr">
+      <c r="N59" s="77" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O59" s="80" t="str"/>
-      <c r="P59" s="77" t="inlineStr">
+      <c r="O59" s="77" t="str"/>
+      <c r="P59" s="79" t="inlineStr">
         <is>
           <t>low</t>
         </is>
@@ -8608,7 +11979,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="U59" s="79">
+      <c r="U59" s="76">
         <f>IF(AND(M59&lt;&gt;"",T59&lt;&gt;""),M59/T59,"")</f>
         <v/>
       </c>
@@ -8704,7 +12075,7 @@
         </is>
       </c>
       <c r="O60" s="75" t="str"/>
-      <c r="P60" s="77" t="inlineStr">
+      <c r="P60" s="79" t="inlineStr">
         <is>
           <t>low</t>
         </is>
@@ -8724,7 +12095,7 @@
           <t>med</t>
         </is>
       </c>
-      <c r="T60" s="78" t="inlineStr">
+      <c r="T60" s="80" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -8805,27 +12176,27 @@
           <t>Смешанные бизнес-задачи</t>
         </is>
       </c>
-      <c r="K61" s="79" t="inlineStr">
+      <c r="K61" s="76" t="inlineStr">
         <is>
           <t>45000</t>
         </is>
       </c>
-      <c r="L61" s="79" t="inlineStr">
+      <c r="L61" s="76" t="inlineStr">
         <is>
           <t>45000</t>
         </is>
       </c>
-      <c r="M61" s="79">
+      <c r="M61" s="76">
         <f>IF(AND(K61&lt;&gt;"",L61&lt;&gt;""),(K61+L61)/2,"")</f>
         <v/>
       </c>
-      <c r="N61" s="80" t="inlineStr">
+      <c r="N61" s="77" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O61" s="80" t="str"/>
-      <c r="P61" s="77" t="inlineStr">
+      <c r="O61" s="77" t="str"/>
+      <c r="P61" s="79" t="inlineStr">
         <is>
           <t>low</t>
         </is>
@@ -8850,7 +12221,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="U61" s="79">
+      <c r="U61" s="76">
         <f>IF(AND(M61&lt;&gt;"",T61&lt;&gt;""),M61/T61,"")</f>
         <v/>
       </c>
@@ -8946,12 +12317,12 @@
         </is>
       </c>
       <c r="O62" s="75" t="str"/>
-      <c r="P62" s="77" t="inlineStr">
+      <c r="P62" s="79" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="Q62" s="77" t="inlineStr">
+      <c r="Q62" s="79" t="inlineStr">
         <is>
           <t>TAKE_WITH_SCOPE</t>
         </is>
@@ -8966,7 +12337,7 @@
           <t>low</t>
         </is>
       </c>
-      <c r="T62" s="78" t="inlineStr">
+      <c r="T62" s="80" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -9047,27 +12418,27 @@
           <t>Смешанные бизнес-задачи</t>
         </is>
       </c>
-      <c r="K63" s="79" t="inlineStr">
+      <c r="K63" s="76" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="L63" s="79" t="inlineStr">
+      <c r="L63" s="76" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="M63" s="79">
+      <c r="M63" s="76">
         <f>IF(AND(K63&lt;&gt;"",L63&lt;&gt;""),(K63+L63)/2,"")</f>
         <v/>
       </c>
-      <c r="N63" s="80" t="inlineStr">
+      <c r="N63" s="77" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="O63" s="80" t="str"/>
-      <c r="P63" s="76" t="inlineStr">
+      <c r="O63" s="77" t="str"/>
+      <c r="P63" s="78" t="inlineStr">
         <is>
           <t>mid</t>
         </is>
@@ -9092,7 +12463,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="U63" s="79">
+      <c r="U63" s="76">
         <f>IF(AND(M63&lt;&gt;"",T63&lt;&gt;""),M63/T63,"")</f>
         <v/>
       </c>
@@ -9188,12 +12559,12 @@
         </is>
       </c>
       <c r="O64" s="75" t="str"/>
-      <c r="P64" s="77" t="inlineStr">
+      <c r="P64" s="79" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="Q64" s="77" t="inlineStr">
+      <c r="Q64" s="79" t="inlineStr">
         <is>
           <t>TAKE_AS_TZ_ONLY</t>
         </is>
@@ -9208,7 +12579,7 @@
           <t>low</t>
         </is>
       </c>
-      <c r="T64" s="78" t="inlineStr">
+      <c r="T64" s="80" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -9289,32 +12660,32 @@
           <t>ТЗ, структура, Gantt</t>
         </is>
       </c>
-      <c r="K65" s="79" t="inlineStr">
+      <c r="K65" s="76" t="inlineStr">
         <is>
           <t>5000</t>
         </is>
       </c>
-      <c r="L65" s="79" t="inlineStr">
+      <c r="L65" s="76" t="inlineStr">
         <is>
           <t>5000</t>
         </is>
       </c>
-      <c r="M65" s="79">
+      <c r="M65" s="76">
         <f>IF(AND(K65&lt;&gt;"",L65&lt;&gt;""),(K65+L65)/2,"")</f>
         <v/>
       </c>
-      <c r="N65" s="80" t="inlineStr">
+      <c r="N65" s="77" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="O65" s="80" t="str"/>
-      <c r="P65" s="76" t="inlineStr">
+      <c r="O65" s="77" t="str"/>
+      <c r="P65" s="78" t="inlineStr">
         <is>
           <t>mid</t>
         </is>
       </c>
-      <c r="Q65" s="77" t="inlineStr">
+      <c r="Q65" s="79" t="inlineStr">
         <is>
           <t>TAKE_FAST</t>
         </is>
@@ -9334,7 +12705,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="U65" s="79">
+      <c r="U65" s="76">
         <f>IF(AND(M65&lt;&gt;"",T65&lt;&gt;""),M65/T65,"")</f>
         <v/>
       </c>
@@ -9430,7 +12801,7 @@
         </is>
       </c>
       <c r="O66" s="75" t="str"/>
-      <c r="P66" s="77" t="inlineStr">
+      <c r="P66" s="79" t="inlineStr">
         <is>
           <t>low</t>
         </is>
@@ -9450,7 +12821,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="T66" s="78" t="inlineStr">
+      <c r="T66" s="80" t="inlineStr">
         <is>
           <t>35</t>
         </is>
@@ -9531,32 +12902,32 @@
           <t>AI, боты, CRM</t>
         </is>
       </c>
-      <c r="K67" s="79" t="inlineStr">
+      <c r="K67" s="76" t="inlineStr">
         <is>
           <t>15000</t>
         </is>
       </c>
-      <c r="L67" s="79" t="inlineStr">
+      <c r="L67" s="76" t="inlineStr">
         <is>
           <t>15000</t>
         </is>
       </c>
-      <c r="M67" s="79">
+      <c r="M67" s="76">
         <f>IF(AND(K67&lt;&gt;"",L67&lt;&gt;""),(K67+L67)/2,"")</f>
         <v/>
       </c>
-      <c r="N67" s="80" t="inlineStr">
+      <c r="N67" s="77" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O67" s="80" t="str"/>
-      <c r="P67" s="77" t="inlineStr">
+      <c r="O67" s="77" t="str"/>
+      <c r="P67" s="79" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="Q67" s="77" t="inlineStr">
+      <c r="Q67" s="79" t="inlineStr">
         <is>
           <t>TAKE</t>
         </is>
@@ -9576,7 +12947,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="U67" s="79">
+      <c r="U67" s="76">
         <f>IF(AND(M67&lt;&gt;"",T67&lt;&gt;""),M67/T67,"")</f>
         <v/>
       </c>
@@ -9672,12 +13043,12 @@
         </is>
       </c>
       <c r="O68" s="75" t="str"/>
-      <c r="P68" s="77" t="inlineStr">
+      <c r="P68" s="79" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="Q68" s="77" t="inlineStr">
+      <c r="Q68" s="79" t="inlineStr">
         <is>
           <t>TAKE</t>
         </is>
@@ -9692,7 +13063,7 @@
           <t>low</t>
         </is>
       </c>
-      <c r="T68" s="78" t="inlineStr">
+      <c r="T68" s="80" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -9773,32 +13144,32 @@
           <t>B2B, КП, лиды</t>
         </is>
       </c>
-      <c r="K69" s="79" t="inlineStr">
+      <c r="K69" s="76" t="inlineStr">
         <is>
           <t>30000</t>
         </is>
       </c>
-      <c r="L69" s="79" t="inlineStr">
+      <c r="L69" s="76" t="inlineStr">
         <is>
           <t>30000</t>
         </is>
       </c>
-      <c r="M69" s="79">
+      <c r="M69" s="76">
         <f>IF(AND(K69&lt;&gt;"",L69&lt;&gt;""),(K69+L69)/2,"")</f>
         <v/>
       </c>
-      <c r="N69" s="80" t="inlineStr">
+      <c r="N69" s="77" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O69" s="80" t="str"/>
-      <c r="P69" s="77" t="inlineStr">
+      <c r="O69" s="77" t="str"/>
+      <c r="P69" s="79" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="Q69" s="77" t="inlineStr">
+      <c r="Q69" s="79" t="inlineStr">
         <is>
           <t>TAKE</t>
         </is>
@@ -9818,7 +13189,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="U69" s="79">
+      <c r="U69" s="76">
         <f>IF(AND(M69&lt;&gt;"",T69&lt;&gt;""),M69/T69,"")</f>
         <v/>
       </c>
@@ -9914,12 +13285,12 @@
         </is>
       </c>
       <c r="O70" s="75" t="str"/>
-      <c r="P70" s="77" t="inlineStr">
+      <c r="P70" s="79" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="Q70" s="77" t="inlineStr">
+      <c r="Q70" s="79" t="inlineStr">
         <is>
           <t>TAKE_DISCOVERY_ONLY</t>
         </is>
@@ -9934,7 +13305,7 @@
           <t>low</t>
         </is>
       </c>
-      <c r="T70" s="78" t="inlineStr">
+      <c r="T70" s="80" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -10015,32 +13386,32 @@
           <t>B2B, КП, лиды</t>
         </is>
       </c>
-      <c r="K71" s="79" t="inlineStr">
+      <c r="K71" s="76" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="L71" s="79" t="inlineStr">
+      <c r="L71" s="76" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="M71" s="79">
+      <c r="M71" s="76">
         <f>IF(AND(K71&lt;&gt;"",L71&lt;&gt;""),(K71+L71)/2,"")</f>
         <v/>
       </c>
-      <c r="N71" s="80" t="inlineStr">
+      <c r="N71" s="77" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="O71" s="80" t="str"/>
-      <c r="P71" s="77" t="inlineStr">
+      <c r="O71" s="77" t="str"/>
+      <c r="P71" s="79" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="Q71" s="77" t="inlineStr">
+      <c r="Q71" s="79" t="inlineStr">
         <is>
           <t>TAKE_TEST</t>
         </is>
@@ -10060,7 +13431,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="U71" s="79">
+      <c r="U71" s="76">
         <f>IF(AND(M71&lt;&gt;"",T71&lt;&gt;""),M71/T71,"")</f>
         <v/>
       </c>
@@ -10156,12 +13527,12 @@
         </is>
       </c>
       <c r="O72" s="75" t="str"/>
-      <c r="P72" s="77" t="inlineStr">
+      <c r="P72" s="79" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="Q72" s="77" t="inlineStr">
+      <c r="Q72" s="79" t="inlineStr">
         <is>
           <t>TAKE_ONLY_FAST</t>
         </is>
@@ -10176,7 +13547,7 @@
           <t>low</t>
         </is>
       </c>
-      <c r="T72" s="78" t="inlineStr">
+      <c r="T72" s="80" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -10257,32 +13628,32 @@
           <t>Excel и таблицы</t>
         </is>
       </c>
-      <c r="K73" s="79" t="inlineStr">
+      <c r="K73" s="76" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
       </c>
-      <c r="L73" s="79" t="inlineStr">
+      <c r="L73" s="76" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
       </c>
-      <c r="M73" s="79">
+      <c r="M73" s="76">
         <f>IF(AND(K73&lt;&gt;"",L73&lt;&gt;""),(K73+L73)/2,"")</f>
         <v/>
       </c>
-      <c r="N73" s="80" t="inlineStr">
+      <c r="N73" s="77" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="O73" s="80" t="str"/>
-      <c r="P73" s="76" t="inlineStr">
+      <c r="O73" s="77" t="str"/>
+      <c r="P73" s="78" t="inlineStr">
         <is>
           <t>mid</t>
         </is>
       </c>
-      <c r="Q73" s="77" t="inlineStr">
+      <c r="Q73" s="79" t="inlineStr">
         <is>
           <t>TAKE_FAST</t>
         </is>
@@ -10302,7 +13673,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="U73" s="79">
+      <c r="U73" s="76">
         <f>IF(AND(M73&lt;&gt;"",T73&lt;&gt;""),M73/T73,"")</f>
         <v/>
       </c>
@@ -10398,12 +13769,12 @@
         </is>
       </c>
       <c r="O74" s="75" t="str"/>
-      <c r="P74" s="77" t="inlineStr">
+      <c r="P74" s="79" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="Q74" s="77" t="inlineStr">
+      <c r="Q74" s="79" t="inlineStr">
         <is>
           <t>TAKE_IF_PLUGIN</t>
         </is>
@@ -10418,7 +13789,7 @@
           <t>med</t>
         </is>
       </c>
-      <c r="T74" s="78" t="inlineStr">
+      <c r="T74" s="80" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -10499,27 +13870,27 @@
           <t>Web, WordPress, SEO</t>
         </is>
       </c>
-      <c r="K75" s="79" t="inlineStr">
+      <c r="K75" s="76" t="inlineStr">
         <is>
           <t>30000</t>
         </is>
       </c>
-      <c r="L75" s="79" t="inlineStr">
+      <c r="L75" s="76" t="inlineStr">
         <is>
           <t>30000</t>
         </is>
       </c>
-      <c r="M75" s="79">
+      <c r="M75" s="76">
         <f>IF(AND(K75&lt;&gt;"",L75&lt;&gt;""),(K75+L75)/2,"")</f>
         <v/>
       </c>
-      <c r="N75" s="80" t="inlineStr">
+      <c r="N75" s="77" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O75" s="80" t="str"/>
-      <c r="P75" s="77" t="inlineStr">
+      <c r="O75" s="77" t="str"/>
+      <c r="P75" s="79" t="inlineStr">
         <is>
           <t>low</t>
         </is>
@@ -10544,7 +13915,7 @@
           <t>35</t>
         </is>
       </c>
-      <c r="U75" s="79">
+      <c r="U75" s="76">
         <f>IF(AND(M75&lt;&gt;"",T75&lt;&gt;""),M75/T75,"")</f>
         <v/>
       </c>
@@ -10640,12 +14011,12 @@
         </is>
       </c>
       <c r="O76" s="75" t="str"/>
-      <c r="P76" s="77" t="inlineStr">
+      <c r="P76" s="79" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="Q76" s="77" t="inlineStr">
+      <c r="Q76" s="79" t="inlineStr">
         <is>
           <t>TAKE_FAST</t>
         </is>
@@ -10660,7 +14031,7 @@
           <t>low</t>
         </is>
       </c>
-      <c r="T76" s="78" t="inlineStr">
+      <c r="T76" s="80" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -10741,32 +14112,32 @@
           <t>Web, WordPress, SEO</t>
         </is>
       </c>
-      <c r="K77" s="79" t="inlineStr">
+      <c r="K77" s="76" t="inlineStr">
         <is>
           <t>6000</t>
         </is>
       </c>
-      <c r="L77" s="79" t="inlineStr">
+      <c r="L77" s="76" t="inlineStr">
         <is>
           <t>6000</t>
         </is>
       </c>
-      <c r="M77" s="79">
+      <c r="M77" s="76">
         <f>IF(AND(K77&lt;&gt;"",L77&lt;&gt;""),(K77+L77)/2,"")</f>
         <v/>
       </c>
-      <c r="N77" s="80" t="inlineStr">
+      <c r="N77" s="77" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O77" s="80" t="str"/>
-      <c r="P77" s="77" t="inlineStr">
+      <c r="O77" s="77" t="str"/>
+      <c r="P77" s="79" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="Q77" s="77" t="inlineStr">
+      <c r="Q77" s="79" t="inlineStr">
         <is>
           <t>TAKE</t>
         </is>
@@ -10786,7 +14157,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="U77" s="79">
+      <c r="U77" s="76">
         <f>IF(AND(M77&lt;&gt;"",T77&lt;&gt;""),M77/T77,"")</f>
         <v/>
       </c>
@@ -10882,7 +14253,7 @@
         </is>
       </c>
       <c r="O78" s="75" t="str"/>
-      <c r="P78" s="77" t="inlineStr">
+      <c r="P78" s="79" t="inlineStr">
         <is>
           <t>low</t>
         </is>
@@ -10902,7 +14273,7 @@
           <t>med</t>
         </is>
       </c>
-      <c r="T78" s="78" t="inlineStr">
+      <c r="T78" s="80" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -10983,32 +14354,32 @@
           <t>Web, WordPress, SEO</t>
         </is>
       </c>
-      <c r="K79" s="79" t="inlineStr">
+      <c r="K79" s="76" t="inlineStr">
         <is>
           <t>6000</t>
         </is>
       </c>
-      <c r="L79" s="79" t="inlineStr">
+      <c r="L79" s="76" t="inlineStr">
         <is>
           <t>6000</t>
         </is>
       </c>
-      <c r="M79" s="79">
+      <c r="M79" s="76">
         <f>IF(AND(K79&lt;&gt;"",L79&lt;&gt;""),(K79+L79)/2,"")</f>
         <v/>
       </c>
-      <c r="N79" s="80" t="inlineStr">
+      <c r="N79" s="77" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O79" s="80" t="str"/>
-      <c r="P79" s="76" t="inlineStr">
+      <c r="O79" s="77" t="str"/>
+      <c r="P79" s="78" t="inlineStr">
         <is>
           <t>mid</t>
         </is>
       </c>
-      <c r="Q79" s="77" t="inlineStr">
+      <c r="Q79" s="79" t="inlineStr">
         <is>
           <t>TAKE_TEST</t>
         </is>
@@ -11028,7 +14399,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="U79" s="79">
+      <c r="U79" s="76">
         <f>IF(AND(M79&lt;&gt;"",T79&lt;&gt;""),M79/T79,"")</f>
         <v/>
       </c>
@@ -11124,7 +14495,7 @@
         </is>
       </c>
       <c r="O80" s="75" t="str"/>
-      <c r="P80" s="76" t="inlineStr">
+      <c r="P80" s="78" t="inlineStr">
         <is>
           <t>mid</t>
         </is>
@@ -11144,7 +14515,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="T80" s="78" t="inlineStr">
+      <c r="T80" s="80" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -11188,7 +14559,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11358,7 +14729,7 @@
           <t>44</t>
         </is>
       </c>
-      <c r="M2" s="77" t="inlineStr">
+      <c r="M2" s="79" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -11395,52 +14766,52 @@
           <t>mixed</t>
         </is>
       </c>
-      <c r="D3" s="80" t="inlineStr">
+      <c r="D3" s="77" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E3" s="80" t="inlineStr">
+      <c r="E3" s="77" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F3" s="80" t="inlineStr">
+      <c r="F3" s="77" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G3" s="79" t="inlineStr">
+      <c r="G3" s="76" t="inlineStr">
         <is>
           <t>180000</t>
         </is>
       </c>
-      <c r="H3" s="80" t="inlineStr">
+      <c r="H3" s="77" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I3" s="80" t="inlineStr">
+      <c r="I3" s="77" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J3" s="80" t="inlineStr">
+      <c r="J3" s="77" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K3" s="80" t="inlineStr">
+      <c r="K3" s="77" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="L3" s="80" t="inlineStr">
+      <c r="L3" s="77" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="M3" s="76" t="inlineStr">
+      <c r="M3" s="78" t="inlineStr">
         <is>
           <t>MIXED: Vlad active, Nastya vitrine</t>
         </is>
@@ -11522,7 +14893,7 @@
           <t>34</t>
         </is>
       </c>
-      <c r="M4" s="77" t="inlineStr">
+      <c r="M4" s="79" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -11559,52 +14930,52 @@
           <t>active_exchange</t>
         </is>
       </c>
-      <c r="D5" s="80" t="inlineStr">
+      <c r="D5" s="77" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E5" s="80" t="inlineStr">
+      <c r="E5" s="77" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="F5" s="80" t="inlineStr">
+      <c r="F5" s="77" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" s="79" t="inlineStr">
+      <c r="G5" s="76" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="H5" s="80" t="inlineStr">
+      <c r="H5" s="77" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="I5" s="80" t="inlineStr">
+      <c r="I5" s="77" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J5" s="80" t="inlineStr">
+      <c r="J5" s="77" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K5" s="80" t="inlineStr">
+      <c r="K5" s="77" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="L5" s="80" t="inlineStr">
+      <c r="L5" s="77" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="M5" s="77" t="inlineStr">
+      <c r="M5" s="79" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -11686,7 +15057,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="M6" s="77" t="inlineStr">
+      <c r="M6" s="79" t="inlineStr">
         <is>
           <t>TAKE</t>
         </is>
@@ -11723,52 +15094,52 @@
           <t>active_exchange</t>
         </is>
       </c>
-      <c r="D7" s="80" t="inlineStr">
+      <c r="D7" s="77" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" s="80" t="inlineStr">
+      <c r="E7" s="77" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F7" s="80" t="inlineStr">
+      <c r="F7" s="77" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" s="79" t="inlineStr">
+      <c r="G7" s="76" t="inlineStr">
         <is>
           <t>21000</t>
         </is>
       </c>
-      <c r="H7" s="80" t="inlineStr">
+      <c r="H7" s="77" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I7" s="80" t="inlineStr">
+      <c r="I7" s="77" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J7" s="80" t="inlineStr">
+      <c r="J7" s="77" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="K7" s="80" t="inlineStr">
+      <c r="K7" s="77" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="L7" s="80" t="inlineStr">
+      <c r="L7" s="77" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="M7" s="77" t="inlineStr">
+      <c r="M7" s="79" t="inlineStr">
         <is>
           <t>TAKE</t>
         </is>
@@ -11850,7 +15221,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="M8" s="77" t="inlineStr">
+      <c r="M8" s="79" t="inlineStr">
         <is>
           <t>TAKE</t>
         </is>
@@ -11887,48 +15258,48 @@
           <t>active_exchange</t>
         </is>
       </c>
-      <c r="D9" s="80" t="inlineStr">
+      <c r="D9" s="77" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E9" s="80" t="inlineStr">
+      <c r="E9" s="77" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="80" t="inlineStr">
+      <c r="F9" s="77" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G9" s="79" t="inlineStr">
+      <c r="G9" s="76" t="inlineStr">
         <is>
           <t>90000</t>
         </is>
       </c>
-      <c r="H9" s="80" t="str"/>
-      <c r="I9" s="80" t="inlineStr">
+      <c r="H9" s="77" t="str"/>
+      <c r="I9" s="77" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J9" s="80" t="inlineStr">
+      <c r="J9" s="77" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K9" s="80" t="inlineStr">
+      <c r="K9" s="77" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="L9" s="80" t="inlineStr">
+      <c r="L9" s="77" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="M9" s="77" t="inlineStr">
+      <c r="M9" s="79" t="inlineStr">
         <is>
           <t>TAKE</t>
         </is>
@@ -12010,7 +15381,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="M10" s="76" t="inlineStr">
+      <c r="M10" s="78" t="inlineStr">
         <is>
           <t>PARITY</t>
         </is>
@@ -12047,48 +15418,48 @@
           <t>vitrine</t>
         </is>
       </c>
-      <c r="D11" s="80" t="inlineStr">
+      <c r="D11" s="77" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E11" s="80" t="inlineStr">
+      <c r="E11" s="77" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="80" t="inlineStr">
+      <c r="F11" s="77" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G11" s="79" t="inlineStr">
+      <c r="G11" s="76" t="inlineStr">
         <is>
           <t>9000</t>
         </is>
       </c>
-      <c r="H11" s="80" t="str"/>
-      <c r="I11" s="80" t="inlineStr">
+      <c r="H11" s="77" t="str"/>
+      <c r="I11" s="77" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J11" s="80" t="inlineStr">
+      <c r="J11" s="77" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K11" s="80" t="inlineStr">
+      <c r="K11" s="77" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L11" s="80" t="inlineStr">
+      <c r="L11" s="77" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="M11" s="76" t="inlineStr">
+      <c r="M11" s="78" t="inlineStr">
         <is>
           <t>PARITY</t>
         </is>
@@ -12197,7 +15568,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -24122,434 +27493,706 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" style="14" min="1" max="1"/>
-    <col width="16" customWidth="1" style="14" min="2" max="2"/>
-    <col width="44" customWidth="1" style="14" min="3" max="3"/>
-    <col width="17" customWidth="1" style="14" min="4" max="4"/>
-    <col width="30" customWidth="1" style="14" min="5" max="5"/>
-    <col width="32" customWidth="1" style="14" min="6" max="6"/>
-    <col width="39" customWidth="1" style="14" min="7" max="7"/>
+    <col width="11" customWidth="1" style="14" min="1" max="1"/>
+    <col width="44" customWidth="1" style="14" min="2" max="2"/>
+    <col width="23" customWidth="1" style="14" min="3" max="3"/>
+    <col width="44" customWidth="1" style="14" min="4" max="4"/>
+    <col width="20" customWidth="1" style="14" min="5" max="5"/>
+    <col width="17" customWidth="1" style="14" min="6" max="6"/>
+    <col width="33" customWidth="1" style="14" min="7" max="7"/>
+    <col width="16" customWidth="1" style="14" min="8" max="8"/>
+    <col width="44" customWidth="1" style="14" min="9" max="9"/>
+    <col width="43" customWidth="1" style="14" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="14">
       <c r="A1" s="72" t="inlineStr">
         <is>
-          <t>path</t>
+          <t>source_id</t>
         </is>
       </c>
       <c r="B1" s="72" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>file</t>
         </is>
       </c>
       <c r="C1" s="72" t="inlineStr">
         <is>
-          <t>decision</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D1" s="72" t="inlineStr">
         <is>
+          <t>method</t>
+        </is>
+      </c>
+      <c r="E1" s="72" t="inlineStr">
+        <is>
+          <t>layer</t>
+        </is>
+      </c>
+      <c r="F1" s="72" t="inlineStr">
+        <is>
           <t>rows_or_sheets</t>
         </is>
       </c>
-      <c r="E1" s="72" t="inlineStr">
-        <is>
-          <t>freshness</t>
-        </is>
-      </c>
-      <c r="F1" s="72" t="inlineStr">
-        <is>
-          <t>role</t>
-        </is>
-      </c>
       <c r="G1" s="72" t="inlineStr">
         <is>
-          <t>use_rule</t>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="H1" s="72" t="inlineStr">
+        <is>
+          <t>do_not_rewrite</t>
+        </is>
+      </c>
+      <c r="I1" s="72" t="inlineStr">
+        <is>
+          <t>how_used</t>
+        </is>
+      </c>
+      <c r="J1" s="72" t="inlineStr">
+        <is>
+          <t>notes</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" s="14">
       <c r="A2" s="73" t="inlineStr">
         <is>
+          <t>S001</t>
+        </is>
+      </c>
+      <c r="B2" s="73" t="inlineStr">
+        <is>
           <t>market/2026-06-kwork-orders-ledger-LIVE.csv</t>
         </is>
       </c>
-      <c r="B2" s="73" t="inlineStr">
-        <is>
-          <t>live_orders</t>
-        </is>
-      </c>
       <c r="C2" s="73" t="inlineStr">
         <is>
-          <t>take as strongest demand signal</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D2" s="73" t="inlineStr">
         <is>
+          <t>logged-in session vladsheimo; window.stateData.wants; kwork_count=offers; priceLimit=budget; views_dirty=views</t>
+        </is>
+      </c>
+      <c r="E2" s="73" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="F2" s="73" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="E2" s="73" t="inlineStr">
-        <is>
-          <t>2026-06-16 logged-in session</t>
-        </is>
-      </c>
-      <c r="F2" s="73" t="inlineStr">
-        <is>
-          <t>fresh demand, offers, views</t>
-        </is>
-      </c>
       <c r="G2" s="73" t="inlineStr">
         <is>
-          <t>can influence canon directly</t>
+          <t>source, do not rewrite</t>
+        </is>
+      </c>
+      <c r="H2" s="73" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I2" s="73" t="inlineStr">
+        <is>
+          <t>strongest demand signal; also separate sheet Живой слой 16.06</t>
+        </is>
+      </c>
+      <c r="J2" s="73" t="inlineStr">
+        <is>
+          <t>kept separate from May/old scrape</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="14">
       <c r="A3" s="71" t="inlineStr">
         <is>
+          <t>S002</t>
+        </is>
+      </c>
+      <c r="B3" s="71" t="inlineStr">
+        <is>
           <t>market/2026-06-market-reality-LIVE.md</t>
         </is>
       </c>
-      <c r="B3" s="71" t="inlineStr">
-        <is>
-          <t>live_memo</t>
-        </is>
-      </c>
       <c r="C3" s="71" t="inlineStr">
         <is>
-          <t>take as live interpretation with debt labels</t>
-        </is>
-      </c>
-      <c r="D3" s="71" t="str"/>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="D3" s="71" t="inlineStr">
+        <is>
+          <t>Claude live memo after logged-in Kwork pass</t>
+        </is>
+      </c>
       <c r="E3" s="71" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="F3" s="71" t="inlineStr">
-        <is>
-          <t>updates market split</t>
-        </is>
-      </c>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="F3" s="71" t="str"/>
       <c r="G3" s="71" t="inlineStr">
         <is>
-          <t>can influence canon directly</t>
+          <t>source, do not rewrite</t>
+        </is>
+      </c>
+      <c r="H3" s="71" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I3" s="71" t="inlineStr">
+        <is>
+          <t>interpretation layer and debt labels</t>
+        </is>
+      </c>
+      <c r="J3" s="71" t="inlineStr">
+        <is>
+          <t>commission/competitors marked ПРОВЕРИТЬ</t>
         </is>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="14">
       <c r="A4" s="73" t="inlineStr">
         <is>
-          <t>market/2026-06-kwork-orders-ledger.csv</t>
+          <t>S003</t>
         </is>
       </c>
       <c r="B4" s="73" t="inlineStr">
         <is>
-          <t>codex_orders</t>
+          <t>market/2026-06-kwork-market-fit-LIVE.xlsx</t>
         </is>
       </c>
       <c r="C4" s="73" t="inlineStr">
         <is>
-          <t>take with caution</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D4" s="73" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>Claude live workbook artifact</t>
         </is>
       </c>
       <c r="E4" s="73" t="inlineStr">
         <is>
-          <t>2026-06-16 public/manual</t>
+          <t>LIVE</t>
         </is>
       </c>
       <c r="F4" s="73" t="inlineStr">
         <is>
-          <t>fit/risk/hours</t>
+          <t>3 sheets</t>
         </is>
       </c>
       <c r="G4" s="73" t="inlineStr">
         <is>
-          <t>can influence canon directly</t>
+          <t>source artifact, do not rewrite</t>
+        </is>
+      </c>
+      <c r="H4" s="73" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I4" s="73" t="inlineStr">
+        <is>
+          <t>cross-check source only</t>
+        </is>
+      </c>
+      <c r="J4" s="73" t="inlineStr">
+        <is>
+          <t>not merged into raw values</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="14">
       <c r="A5" s="71" t="inlineStr">
         <is>
-          <t>market/2026-06-competitor-ledger.csv</t>
+          <t>S004</t>
         </is>
       </c>
       <c r="B5" s="71" t="inlineStr">
         <is>
-          <t>competitors</t>
+          <t>market/2026-06-kwork-market-fit-LIVE.pptx</t>
         </is>
       </c>
       <c r="C5" s="71" t="inlineStr">
         <is>
-          <t>use with caution</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D5" s="71" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>Claude live slides artifact</t>
         </is>
       </c>
       <c r="E5" s="71" t="inlineStr">
         <is>
-          <t>2026-05-27/2026-06-16 mixed</t>
+          <t>LIVE</t>
         </is>
       </c>
       <c r="F5" s="71" t="inlineStr">
         <is>
-          <t>historic competitor shape</t>
+          <t>deck</t>
         </is>
       </c>
       <c r="G5" s="71" t="inlineStr">
         <is>
-          <t>patterns yes, exact current claims no</t>
+          <t>source artifact, do not rewrite</t>
+        </is>
+      </c>
+      <c r="H5" s="71" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I5" s="71" t="inlineStr">
+        <is>
+          <t>presentation source only</t>
+        </is>
+      </c>
+      <c r="J5" s="71" t="inlineStr">
+        <is>
+          <t>not used for row arithmetic</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="14">
       <c r="A6" s="73" t="inlineStr">
         <is>
-          <t>market/2026-06-kwork-market-fit-LIVE.xlsx</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="B6" s="73" t="inlineStr">
         <is>
-          <t>live_workbook</t>
+          <t>market/2026-06-kwork-orders-ledger.csv</t>
         </is>
       </c>
       <c r="C6" s="73" t="inlineStr">
         <is>
-          <t>take as source artifact</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D6" s="73" t="inlineStr">
         <is>
-          <t>3 sheets</t>
+          <t>Codex manual/public ledger before LIVE update</t>
         </is>
       </c>
       <c r="E6" s="73" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>CODEX</t>
         </is>
       </c>
       <c r="F6" s="73" t="inlineStr">
         <is>
-          <t>live workbook from Claude lane</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G6" s="73" t="inlineStr">
         <is>
-          <t>can influence canon directly</t>
+          <t>use with caution</t>
+        </is>
+      </c>
+      <c r="H6" s="73" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I6" s="73" t="inlineStr">
+        <is>
+          <t>fit/risk/hours and old order rows</t>
+        </is>
+      </c>
+      <c r="J6" s="73" t="inlineStr">
+        <is>
+          <t>lower freshness than LIVE</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="14">
       <c r="A7" s="71" t="inlineStr">
         <is>
-          <t>market/2026-06-kwork-market-fit.xlsx</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="B7" s="71" t="inlineStr">
         <is>
-          <t>codex_workbook</t>
+          <t>market/2026-06-competitor-ledger.csv</t>
         </is>
       </c>
       <c r="C7" s="71" t="inlineStr">
         <is>
-          <t>take as source artifact</t>
+          <t>2026-05-27/2026-06-16</t>
         </is>
       </c>
       <c r="D7" s="71" t="inlineStr">
         <is>
-          <t>5 sheets</t>
+          <t>historic competitor notes, not fresh vitrine scrape</t>
         </is>
       </c>
       <c r="E7" s="71" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>COMPETITOR_ARCHIVE</t>
         </is>
       </c>
       <c r="F7" s="71" t="inlineStr">
         <is>
-          <t>previous workbook</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G7" s="71" t="inlineStr">
         <is>
-          <t>can influence canon directly</t>
+          <t>ПРОВЕРИТЬ/обновить</t>
+        </is>
+      </c>
+      <c r="H7" s="71" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I7" s="71" t="inlineStr">
+        <is>
+          <t>shape of competition only</t>
+        </is>
+      </c>
+      <c r="J7" s="71" t="inlineStr">
+        <is>
+          <t>fresh competitor cards were not captured</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="14">
       <c r="A8" s="73" t="inlineStr">
         <is>
-          <t>spouse_kwork/05_KWORK_FULL_COPY_CARDS_RU.md</t>
+          <t>S007</t>
         </is>
       </c>
       <c r="B8" s="73" t="inlineStr">
         <is>
-          <t>copy_cards</t>
+          <t>market/2026-06-kwork-market-fit.xlsx</t>
         </is>
       </c>
       <c r="C8" s="73" t="inlineStr">
         <is>
-          <t>rebuild</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D8" s="73" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>previous Codex workbook artifact</t>
         </is>
       </c>
       <c r="E8" s="73" t="inlineStr">
         <is>
-          <t>pre-live</t>
+          <t>CODEX</t>
         </is>
       </c>
       <c r="F8" s="73" t="inlineStr">
         <is>
-          <t>full field structure</t>
+          <t>5 sheets</t>
         </is>
       </c>
       <c r="G8" s="73" t="inlineStr">
         <is>
-          <t>structure yes, final copy no</t>
+          <t>source artifact</t>
+        </is>
+      </c>
+      <c r="H8" s="73" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I8" s="73" t="inlineStr">
+        <is>
+          <t>base workbook comparison</t>
+        </is>
+      </c>
+      <c r="J8" s="73" t="inlineStr">
+        <is>
+          <t>superseded by CANON</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="14">
       <c r="A9" s="71" t="inlineStr">
         <is>
-          <t>vlad_kwork/2026-06-kwork-cards-draft.md</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="B9" s="71" t="inlineStr">
         <is>
-          <t>copy_cards</t>
+          <t>market/2026-06-kwork-market-fit.pptx</t>
         </is>
       </c>
       <c r="C9" s="71" t="inlineStr">
         <is>
-          <t>expand</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D9" s="71" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>previous Codex deck artifact</t>
         </is>
       </c>
       <c r="E9" s="71" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>CODEX</t>
         </is>
       </c>
       <c r="F9" s="71" t="inlineStr">
         <is>
-          <t>Vlad top draft</t>
+          <t>deck</t>
         </is>
       </c>
       <c r="G9" s="71" t="inlineStr">
         <is>
-          <t>structure yes, final copy no</t>
+          <t>source artifact</t>
+        </is>
+      </c>
+      <c r="H9" s="71" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I9" s="71" t="inlineStr">
+        <is>
+          <t>presentation comparison</t>
+        </is>
+      </c>
+      <c r="J9" s="71" t="inlineStr">
+        <is>
+          <t>superseded by CANON</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="14">
       <c r="A10" s="73" t="inlineStr">
         <is>
-          <t>vsheimo profile/vsheimo/kwork/kwork_services_pack_v3_more_factual.xlsx</t>
+          <t>S009</t>
         </is>
       </c>
       <c r="B10" s="73" t="inlineStr">
         <is>
-          <t>archive_cards</t>
+          <t>spouse_kwork/05_KWORK_FULL_COPY_CARDS_RU.md</t>
         </is>
       </c>
       <c r="C10" s="73" t="inlineStr">
         <is>
-          <t>use as idea bank</t>
+          <t>pre-live</t>
         </is>
       </c>
       <c r="D10" s="73" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>manual Kwork copy package for Nastya</t>
         </is>
       </c>
       <c r="E10" s="73" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>KWORK_COPY</t>
         </is>
       </c>
       <c r="F10" s="73" t="inlineStr">
         <is>
-          <t>32 Vlad service ideas</t>
+          <t>182</t>
         </is>
       </c>
       <c r="G10" s="73" t="inlineStr">
         <is>
-          <t>supporting material</t>
+          <t>rebuild, not dogma</t>
+        </is>
+      </c>
+      <c r="H10" s="73" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I10" s="73" t="inlineStr">
+        <is>
+          <t>field structure for Kwork cards</t>
+        </is>
+      </c>
+      <c r="J10" s="73" t="inlineStr">
+        <is>
+          <t>copy must be rewritten after market canon</t>
         </is>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="14">
       <c r="A11" s="71" t="inlineStr">
         <is>
+          <t>S010</t>
+        </is>
+      </c>
+      <c r="B11" s="71" t="inlineStr">
+        <is>
+          <t>vlad_kwork/2026-06-kwork-cards-draft.md</t>
+        </is>
+      </c>
+      <c r="C11" s="71" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="D11" s="71" t="inlineStr">
+        <is>
+          <t>Codex draft Kwork cards for Vlad</t>
+        </is>
+      </c>
+      <c r="E11" s="71" t="inlineStr">
+        <is>
+          <t>KWORK_COPY</t>
+        </is>
+      </c>
+      <c r="F11" s="71" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G11" s="71" t="inlineStr">
+        <is>
+          <t>expand/rebuild</t>
+        </is>
+      </c>
+      <c r="H11" s="71" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I11" s="71" t="inlineStr">
+        <is>
+          <t>Vlad card idea bank</t>
+        </is>
+      </c>
+      <c r="J11" s="71" t="inlineStr">
+        <is>
+          <t>not final copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1" s="14">
+      <c r="A12" s="73" t="inlineStr">
+        <is>
+          <t>S011</t>
+        </is>
+      </c>
+      <c r="B12" s="73" t="inlineStr">
+        <is>
+          <t>vsheimo profile/vsheimo/kwork/kwork_services_pack_v3_more_factual.xlsx</t>
+        </is>
+      </c>
+      <c r="C12" s="73" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="D12" s="73" t="inlineStr">
+        <is>
+          <t>archive workbook with old 32-service pack</t>
+        </is>
+      </c>
+      <c r="E12" s="73" t="inlineStr">
+        <is>
+          <t>ARCHIVE</t>
+        </is>
+      </c>
+      <c r="F12" s="73" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G12" s="73" t="inlineStr">
+        <is>
+          <t>idea bank only</t>
+        </is>
+      </c>
+      <c r="H12" s="73" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I12" s="73" t="inlineStr">
+        <is>
+          <t>service idea inventory</t>
+        </is>
+      </c>
+      <c r="J12" s="73" t="inlineStr">
+        <is>
+          <t>old claims need proof</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1" s="14">
+      <c r="A13" s="71" t="inlineStr">
+        <is>
+          <t>S012</t>
+        </is>
+      </c>
+      <c r="B13" s="71" t="inlineStr">
+        <is>
           <t>../spreadsheet-cfo-rules-template</t>
         </is>
       </c>
-      <c r="B11" s="71" t="inlineStr">
-        <is>
-          <t>rules</t>
-        </is>
-      </c>
-      <c r="C11" s="71" t="inlineStr">
+      <c r="C13" s="71" t="inlineStr">
+        <is>
+          <t>cloned 2026-06-16</t>
+        </is>
+      </c>
+      <c r="D13" s="71" t="inlineStr">
+        <is>
+          <t>spreadsheet rules repository</t>
+        </is>
+      </c>
+      <c r="E13" s="71" t="inlineStr">
+        <is>
+          <t>RULES</t>
+        </is>
+      </c>
+      <c r="F13" s="71" t="inlineStr">
+        <is>
+          <t>rules+templates</t>
+        </is>
+      </c>
+      <c r="G13" s="71" t="inlineStr">
         <is>
           <t>use as workbook canon</t>
         </is>
       </c>
-      <c r="D11" s="71" t="inlineStr">
-        <is>
-          <t>rules+templates</t>
-        </is>
-      </c>
-      <c r="E11" s="71" t="inlineStr">
-        <is>
-          <t>cloned 2026-06-16</t>
-        </is>
-      </c>
-      <c r="F11" s="71" t="inlineStr">
-        <is>
-          <t>table style and critic pass</t>
-        </is>
-      </c>
-      <c r="G11" s="71" t="inlineStr">
-        <is>
-          <t>supporting material</t>
+      <c r="H13" s="71" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I13" s="71" t="inlineStr">
+        <is>
+          <t>style/source separation/check discipline</t>
+        </is>
+      </c>
+      <c r="J13" s="71" t="inlineStr">
+        <is>
+          <t>rules, not market data</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G11"/>
+  <autoFilter ref="A1:J13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -24679,7 +28322,7 @@
           <t>Nastya proof</t>
         </is>
       </c>
-      <c r="B5" s="76" t="inlineStr">
+      <c r="B5" s="78" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
